--- a/reports/onpage-audit-compat-fishhealth-2026-09-20.xlsx
+++ b/reports/onpage-audit-compat-fishhealth-2026-09-20.xlsx
@@ -33833,10 +33833,8 @@
       <c r="F464" t="n">
         <v>70.8</v>
       </c>
-      <c r="G464" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G464" t="n">
+        <v>80</v>
       </c>
       <c r="H464" t="n">
         <v>86</v>
@@ -33907,10 +33905,8 @@
       <c r="F465" t="n">
         <v>71.5</v>
       </c>
-      <c r="G465" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G465" t="n">
+        <v>80.8</v>
       </c>
       <c r="H465" t="n">
         <v>86</v>
@@ -33981,10 +33977,8 @@
       <c r="F466" t="n">
         <v>71.5</v>
       </c>
-      <c r="G466" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G466" t="n">
+        <v>80.8</v>
       </c>
       <c r="H466" t="n">
         <v>86</v>
@@ -34055,10 +34049,8 @@
       <c r="F467" t="n">
         <v>58.8</v>
       </c>
-      <c r="G467" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G467" t="n">
+        <v>89.7</v>
       </c>
       <c r="H467" t="n">
         <v>58</v>
@@ -34129,10 +34121,8 @@
       <c r="F468" t="n">
         <v>60.4</v>
       </c>
-      <c r="G468" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G468" t="n">
+        <v>67.2</v>
       </c>
       <c r="H468" t="n">
         <v>66</v>
@@ -34203,10 +34193,8 @@
       <c r="F469" t="n">
         <v>60.4</v>
       </c>
-      <c r="G469" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G469" t="n">
+        <v>92.7</v>
       </c>
       <c r="H469" t="n">
         <v>66</v>
@@ -34277,10 +34265,8 @@
       <c r="F470" t="n">
         <v>60.8</v>
       </c>
-      <c r="G470" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G470" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H470" t="n">
         <v>58</v>
@@ -34351,10 +34337,8 @@
       <c r="F471" t="n">
         <v>61.5</v>
       </c>
-      <c r="G471" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G471" t="n">
+        <v>92.7</v>
       </c>
       <c r="H471" t="n">
         <v>66</v>
@@ -34425,10 +34409,8 @@
       <c r="F472" t="n">
         <v>61.9</v>
       </c>
-      <c r="G472" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G472" t="n">
+        <v>67.2</v>
       </c>
       <c r="H472" t="n">
         <v>58</v>
@@ -34499,10 +34481,8 @@
       <c r="F473" t="n">
         <v>61.9</v>
       </c>
-      <c r="G473" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G473" t="n">
+        <v>67.2</v>
       </c>
       <c r="H473" t="n">
         <v>58</v>
@@ -34573,10 +34553,8 @@
       <c r="F474" t="n">
         <v>61.9</v>
       </c>
-      <c r="G474" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G474" t="n">
+        <v>66</v>
       </c>
       <c r="H474" t="n">
         <v>58</v>
@@ -34647,10 +34625,8 @@
       <c r="F475" t="n">
         <v>62.3</v>
       </c>
-      <c r="G475" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G475" t="n">
+        <v>67.2</v>
       </c>
       <c r="H475" t="n">
         <v>66</v>
@@ -34721,10 +34697,8 @@
       <c r="F476" t="n">
         <v>62.3</v>
       </c>
-      <c r="G476" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G476" t="n">
+        <v>92.7</v>
       </c>
       <c r="H476" t="n">
         <v>66</v>
@@ -34795,10 +34769,8 @@
       <c r="F477" t="n">
         <v>63.5</v>
       </c>
-      <c r="G477" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G477" t="n">
+        <v>94.3</v>
       </c>
       <c r="H477" t="n">
         <v>66</v>
@@ -34869,10 +34841,8 @@
       <c r="F478" t="n">
         <v>63.5</v>
       </c>
-      <c r="G478" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G478" t="n">
+        <v>92.7</v>
       </c>
       <c r="H478" t="n">
         <v>66</v>
@@ -34943,10 +34913,8 @@
       <c r="F479" t="n">
         <v>63.5</v>
       </c>
-      <c r="G479" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G479" t="n">
+        <v>67.2</v>
       </c>
       <c r="H479" t="n">
         <v>66</v>
@@ -35017,10 +34985,8 @@
       <c r="F480" t="n">
         <v>63.5</v>
       </c>
-      <c r="G480" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G480" t="n">
+        <v>94.3</v>
       </c>
       <c r="H480" t="n">
         <v>66</v>
@@ -35091,10 +35057,8 @@
       <c r="F481" t="n">
         <v>63.5</v>
       </c>
-      <c r="G481" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G481" t="n">
+        <v>92.7</v>
       </c>
       <c r="H481" t="n">
         <v>66</v>
@@ -35165,10 +35129,8 @@
       <c r="F482" t="n">
         <v>63.5</v>
       </c>
-      <c r="G482" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G482" t="n">
+        <v>92.7</v>
       </c>
       <c r="H482" t="n">
         <v>66</v>
@@ -35239,10 +35201,8 @@
       <c r="F483" t="n">
         <v>63.5</v>
       </c>
-      <c r="G483" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G483" t="n">
+        <v>94.3</v>
       </c>
       <c r="H483" t="n">
         <v>66</v>
@@ -35313,10 +35273,8 @@
       <c r="F484" t="n">
         <v>63.5</v>
       </c>
-      <c r="G484" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G484" t="n">
+        <v>94.3</v>
       </c>
       <c r="H484" t="n">
         <v>66</v>
@@ -35387,10 +35345,8 @@
       <c r="F485" t="n">
         <v>64.2</v>
       </c>
-      <c r="G485" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G485" t="n">
+        <v>89.7</v>
       </c>
       <c r="H485" t="n">
         <v>68</v>
@@ -35461,10 +35417,8 @@
       <c r="F486" t="n">
         <v>64.2</v>
       </c>
-      <c r="G486" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G486" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H486" t="n">
         <v>68</v>
@@ -35535,10 +35489,8 @@
       <c r="F487" t="n">
         <v>65</v>
       </c>
-      <c r="G487" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G487" t="n">
+        <v>94.3</v>
       </c>
       <c r="H487" t="n">
         <v>66</v>
@@ -35609,10 +35561,8 @@
       <c r="F488" t="n">
         <v>65.40000000000001</v>
       </c>
-      <c r="G488" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G488" t="n">
+        <v>94.3</v>
       </c>
       <c r="H488" t="n">
         <v>68</v>
@@ -35683,10 +35633,8 @@
       <c r="F489" t="n">
         <v>65.40000000000001</v>
       </c>
-      <c r="G489" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G489" t="n">
+        <v>88.5</v>
       </c>
       <c r="H489" t="n">
         <v>68</v>
@@ -35757,10 +35705,8 @@
       <c r="F490" t="n">
         <v>65.40000000000001</v>
       </c>
-      <c r="G490" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G490" t="n">
+        <v>92.7</v>
       </c>
       <c r="H490" t="n">
         <v>68</v>
@@ -35831,10 +35777,8 @@
       <c r="F491" t="n">
         <v>65.8</v>
       </c>
-      <c r="G491" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G491" t="n">
+        <v>88.5</v>
       </c>
       <c r="H491" t="n">
         <v>76</v>
@@ -35905,10 +35849,8 @@
       <c r="F492" t="n">
         <v>65.8</v>
       </c>
-      <c r="G492" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G492" t="n">
+        <v>92.7</v>
       </c>
       <c r="H492" t="n">
         <v>68</v>
@@ -35979,10 +35921,8 @@
       <c r="F493" t="n">
         <v>65.8</v>
       </c>
-      <c r="G493" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G493" t="n">
+        <v>88.5</v>
       </c>
       <c r="H493" t="n">
         <v>70</v>
@@ -36053,10 +35993,8 @@
       <c r="F494" t="n">
         <v>65.8</v>
       </c>
-      <c r="G494" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G494" t="n">
+        <v>89.7</v>
       </c>
       <c r="H494" t="n">
         <v>76</v>
@@ -36127,10 +36065,8 @@
       <c r="F495" t="n">
         <v>65.8</v>
       </c>
-      <c r="G495" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G495" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H495" t="n">
         <v>76</v>
@@ -36201,10 +36137,8 @@
       <c r="F496" t="n">
         <v>65.8</v>
       </c>
-      <c r="G496" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G496" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H496" t="n">
         <v>76</v>
@@ -36275,10 +36209,8 @@
       <c r="F497" t="n">
         <v>65.8</v>
       </c>
-      <c r="G497" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G497" t="n">
+        <v>90.09999999999999</v>
       </c>
       <c r="H497" t="n">
         <v>68</v>
@@ -36349,10 +36281,8 @@
       <c r="F498" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="G498" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G498" t="n">
+        <v>88.5</v>
       </c>
       <c r="H498" t="n">
         <v>76</v>
@@ -36423,10 +36353,8 @@
       <c r="F499" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="G499" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G499" t="n">
+        <v>88.5</v>
       </c>
       <c r="H499" t="n">
         <v>76</v>
@@ -36497,10 +36425,8 @@
       <c r="F500" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="G500" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G500" t="n">
+        <v>88.5</v>
       </c>
       <c r="H500" t="n">
         <v>76</v>
@@ -36571,10 +36497,8 @@
       <c r="F501" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="G501" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G501" t="n">
+        <v>88.5</v>
       </c>
       <c r="H501" t="n">
         <v>76</v>
@@ -36645,10 +36569,8 @@
       <c r="F502" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="G502" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G502" t="n">
+        <v>91.2</v>
       </c>
       <c r="H502" t="n">
         <v>68</v>
@@ -36719,10 +36641,8 @@
       <c r="F503" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="G503" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G503" t="n">
+        <v>94.3</v>
       </c>
       <c r="H503" t="n">
         <v>68</v>
@@ -36793,10 +36713,8 @@
       <c r="F504" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="G504" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G504" t="n">
+        <v>88.5</v>
       </c>
       <c r="H504" t="n">
         <v>76</v>
@@ -36867,10 +36785,8 @@
       <c r="F505" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="G505" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G505" t="n">
+        <v>91.2</v>
       </c>
       <c r="H505" t="n">
         <v>68</v>
@@ -36941,10 +36857,8 @@
       <c r="F506" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="G506" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G506" t="n">
+        <v>88.5</v>
       </c>
       <c r="H506" t="n">
         <v>76</v>
@@ -37015,10 +36929,8 @@
       <c r="F507" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="G507" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G507" t="n">
+        <v>88.5</v>
       </c>
       <c r="H507" t="n">
         <v>76</v>
@@ -37089,10 +37001,8 @@
       <c r="F508" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="G508" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G508" t="n">
+        <v>88.5</v>
       </c>
       <c r="H508" t="n">
         <v>76</v>
@@ -37163,10 +37073,8 @@
       <c r="F509" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="G509" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G509" t="n">
+        <v>88.5</v>
       </c>
       <c r="H509" t="n">
         <v>76</v>
@@ -37237,10 +37145,8 @@
       <c r="F510" t="n">
         <v>67.3</v>
       </c>
-      <c r="G510" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G510" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H510" t="n">
         <v>68</v>
@@ -37311,10 +37217,8 @@
       <c r="F511" t="n">
         <v>67.3</v>
       </c>
-      <c r="G511" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G511" t="n">
+        <v>91.2</v>
       </c>
       <c r="H511" t="n">
         <v>76</v>
@@ -37385,10 +37289,8 @@
       <c r="F512" t="n">
         <v>67.3</v>
       </c>
-      <c r="G512" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G512" t="n">
+        <v>90.09999999999999</v>
       </c>
       <c r="H512" t="n">
         <v>70</v>
@@ -37459,10 +37361,8 @@
       <c r="F513" t="n">
         <v>67.3</v>
       </c>
-      <c r="G513" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G513" t="n">
+        <v>91.2</v>
       </c>
       <c r="H513" t="n">
         <v>58</v>
@@ -37533,10 +37433,8 @@
       <c r="F514" t="n">
         <v>67.7</v>
       </c>
-      <c r="G514" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G514" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H514" t="n">
         <v>70</v>
@@ -37607,10 +37505,8 @@
       <c r="F515" t="n">
         <v>68.5</v>
       </c>
-      <c r="G515" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G515" t="n">
+        <v>89.7</v>
       </c>
       <c r="H515" t="n">
         <v>76</v>
@@ -37681,10 +37577,8 @@
       <c r="F516" t="n">
         <v>68.5</v>
       </c>
-      <c r="G516" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G516" t="n">
+        <v>91.2</v>
       </c>
       <c r="H516" t="n">
         <v>76</v>
@@ -37755,10 +37649,8 @@
       <c r="F517" t="n">
         <v>68.5</v>
       </c>
-      <c r="G517" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G517" t="n">
+        <v>94.3</v>
       </c>
       <c r="H517" t="n">
         <v>68</v>
@@ -37829,10 +37721,8 @@
       <c r="F518" t="n">
         <v>68.5</v>
       </c>
-      <c r="G518" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G518" t="n">
+        <v>88.5</v>
       </c>
       <c r="H518" t="n">
         <v>76</v>
@@ -37903,10 +37793,8 @@
       <c r="F519" t="n">
         <v>68.5</v>
       </c>
-      <c r="G519" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G519" t="n">
+        <v>90.09999999999999</v>
       </c>
       <c r="H519" t="n">
         <v>76</v>
@@ -37977,10 +37865,8 @@
       <c r="F520" t="n">
         <v>68.5</v>
       </c>
-      <c r="G520" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G520" t="n">
+        <v>91.2</v>
       </c>
       <c r="H520" t="n">
         <v>76</v>
@@ -38051,10 +37937,8 @@
       <c r="F521" t="n">
         <v>68.5</v>
       </c>
-      <c r="G521" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G521" t="n">
+        <v>91.2</v>
       </c>
       <c r="H521" t="n">
         <v>76</v>
@@ -38125,10 +38009,8 @@
       <c r="F522" t="n">
         <v>68.5</v>
       </c>
-      <c r="G522" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G522" t="n">
+        <v>94.3</v>
       </c>
       <c r="H522" t="n">
         <v>76</v>
@@ -38199,10 +38081,8 @@
       <c r="F523" t="n">
         <v>68.5</v>
       </c>
-      <c r="G523" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G523" t="n">
+        <v>91.2</v>
       </c>
       <c r="H523" t="n">
         <v>76</v>
@@ -38273,10 +38153,8 @@
       <c r="F524" t="n">
         <v>68.5</v>
       </c>
-      <c r="G524" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G524" t="n">
+        <v>91.2</v>
       </c>
       <c r="H524" t="n">
         <v>76</v>
@@ -38347,10 +38225,8 @@
       <c r="F525" t="n">
         <v>68.5</v>
       </c>
-      <c r="G525" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G525" t="n">
+        <v>92.7</v>
       </c>
       <c r="H525" t="n">
         <v>76</v>
@@ -38421,10 +38297,8 @@
       <c r="F526" t="n">
         <v>68.5</v>
       </c>
-      <c r="G526" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G526" t="n">
+        <v>92.7</v>
       </c>
       <c r="H526" t="n">
         <v>68</v>
@@ -38495,10 +38369,8 @@
       <c r="F527" t="n">
         <v>68.5</v>
       </c>
-      <c r="G527" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G527" t="n">
+        <v>92.7</v>
       </c>
       <c r="H527" t="n">
         <v>68</v>
@@ -38569,10 +38441,8 @@
       <c r="F528" t="n">
         <v>68.5</v>
       </c>
-      <c r="G528" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G528" t="n">
+        <v>91.2</v>
       </c>
       <c r="H528" t="n">
         <v>76</v>
@@ -38643,10 +38513,8 @@
       <c r="F529" t="n">
         <v>68.5</v>
       </c>
-      <c r="G529" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G529" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H529" t="n">
         <v>68</v>
@@ -38717,10 +38585,8 @@
       <c r="F530" t="n">
         <v>68.5</v>
       </c>
-      <c r="G530" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G530" t="n">
+        <v>91.2</v>
       </c>
       <c r="H530" t="n">
         <v>76</v>
@@ -38791,10 +38657,8 @@
       <c r="F531" t="n">
         <v>68.5</v>
       </c>
-      <c r="G531" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G531" t="n">
+        <v>91.2</v>
       </c>
       <c r="H531" t="n">
         <v>76</v>
@@ -38865,10 +38729,8 @@
       <c r="F532" t="n">
         <v>68.5</v>
       </c>
-      <c r="G532" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G532" t="n">
+        <v>94.3</v>
       </c>
       <c r="H532" t="n">
         <v>76</v>
@@ -38939,10 +38801,8 @@
       <c r="F533" t="n">
         <v>68.5</v>
       </c>
-      <c r="G533" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G533" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H533" t="n">
         <v>68</v>
@@ -39013,10 +38873,8 @@
       <c r="F534" t="n">
         <v>68.5</v>
       </c>
-      <c r="G534" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G534" t="n">
+        <v>92.7</v>
       </c>
       <c r="H534" t="n">
         <v>68</v>
@@ -39087,10 +38945,8 @@
       <c r="F535" t="n">
         <v>68.5</v>
       </c>
-      <c r="G535" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G535" t="n">
+        <v>92.7</v>
       </c>
       <c r="H535" t="n">
         <v>68</v>
@@ -39161,10 +39017,8 @@
       <c r="F536" t="n">
         <v>68.5</v>
       </c>
-      <c r="G536" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G536" t="n">
+        <v>89.7</v>
       </c>
       <c r="H536" t="n">
         <v>76</v>
@@ -39235,10 +39089,8 @@
       <c r="F537" t="n">
         <v>68.8</v>
       </c>
-      <c r="G537" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G537" t="n">
+        <v>91.2</v>
       </c>
       <c r="H537" t="n">
         <v>66</v>
@@ -39309,10 +39161,8 @@
       <c r="F538" t="n">
         <v>68.8</v>
       </c>
-      <c r="G538" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G538" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H538" t="n">
         <v>76</v>
@@ -39383,10 +39233,8 @@
       <c r="F539" t="n">
         <v>68.8</v>
       </c>
-      <c r="G539" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G539" t="n">
+        <v>94.3</v>
       </c>
       <c r="H539" t="n">
         <v>68</v>
@@ -39457,10 +39305,8 @@
       <c r="F540" t="n">
         <v>68.8</v>
       </c>
-      <c r="G540" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G540" t="n">
+        <v>90.09999999999999</v>
       </c>
       <c r="H540" t="n">
         <v>66</v>
@@ -39531,10 +39377,8 @@
       <c r="F541" t="n">
         <v>68.8</v>
       </c>
-      <c r="G541" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G541" t="n">
+        <v>92.7</v>
       </c>
       <c r="H541" t="n">
         <v>76</v>
@@ -39605,10 +39449,8 @@
       <c r="F542" t="n">
         <v>68.8</v>
       </c>
-      <c r="G542" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G542" t="n">
+        <v>92.7</v>
       </c>
       <c r="H542" t="n">
         <v>76</v>
@@ -39679,10 +39521,8 @@
       <c r="F543" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="G543" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G543" t="n">
+        <v>88.5</v>
       </c>
       <c r="H543" t="n">
         <v>76</v>
@@ -39753,10 +39593,8 @@
       <c r="F544" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="G544" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G544" t="n">
+        <v>92.7</v>
       </c>
       <c r="H544" t="n">
         <v>68</v>
@@ -39827,10 +39665,8 @@
       <c r="F545" t="n">
         <v>70</v>
       </c>
-      <c r="G545" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G545" t="n">
+        <v>92.7</v>
       </c>
       <c r="H545" t="n">
         <v>76</v>
@@ -39901,10 +39737,8 @@
       <c r="F546" t="n">
         <v>70</v>
       </c>
-      <c r="G546" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G546" t="n">
+        <v>94.3</v>
       </c>
       <c r="H546" t="n">
         <v>68</v>
@@ -39975,10 +39809,8 @@
       <c r="F547" t="n">
         <v>70</v>
       </c>
-      <c r="G547" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G547" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H547" t="n">
         <v>76</v>
@@ -40049,10 +39881,8 @@
       <c r="F548" t="n">
         <v>70</v>
       </c>
-      <c r="G548" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G548" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H548" t="n">
         <v>76</v>
@@ -40123,10 +39953,8 @@
       <c r="F549" t="n">
         <v>70</v>
       </c>
-      <c r="G549" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G549" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="H549" t="n">
         <v>76</v>
@@ -40197,10 +40025,8 @@
       <c r="F550" t="n">
         <v>70</v>
       </c>
-      <c r="G550" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G550" t="n">
+        <v>92.7</v>
       </c>
       <c r="H550" t="n">
         <v>76</v>
@@ -40271,10 +40097,8 @@
       <c r="F551" t="n">
         <v>70</v>
       </c>
-      <c r="G551" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G551" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="H551" t="n">
         <v>68</v>
@@ -40345,10 +40169,8 @@
       <c r="F552" t="n">
         <v>70</v>
       </c>
-      <c r="G552" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G552" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="H552" t="n">
         <v>68</v>
@@ -40419,10 +40241,8 @@
       <c r="F553" t="n">
         <v>70</v>
       </c>
-      <c r="G553" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G553" t="n">
+        <v>92.7</v>
       </c>
       <c r="H553" t="n">
         <v>76</v>
@@ -40493,10 +40313,8 @@
       <c r="F554" t="n">
         <v>70</v>
       </c>
-      <c r="G554" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G554" t="n">
+        <v>92.7</v>
       </c>
       <c r="H554" t="n">
         <v>68</v>
@@ -40567,10 +40385,8 @@
       <c r="F555" t="n">
         <v>70</v>
       </c>
-      <c r="G555" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G555" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="H555" t="n">
         <v>76</v>
@@ -40641,10 +40457,8 @@
       <c r="F556" t="n">
         <v>70</v>
       </c>
-      <c r="G556" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G556" t="n">
+        <v>94.3</v>
       </c>
       <c r="H556" t="n">
         <v>68</v>
@@ -40715,10 +40529,8 @@
       <c r="F557" t="n">
         <v>70</v>
       </c>
-      <c r="G557" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G557" t="n">
+        <v>94.3</v>
       </c>
       <c r="H557" t="n">
         <v>68</v>
@@ -40789,10 +40601,8 @@
       <c r="F558" t="n">
         <v>70</v>
       </c>
-      <c r="G558" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G558" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H558" t="n">
         <v>76</v>
@@ -40863,10 +40673,8 @@
       <c r="F559" t="n">
         <v>70</v>
       </c>
-      <c r="G559" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G559" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H559" t="n">
         <v>76</v>
@@ -40937,10 +40745,8 @@
       <c r="F560" t="n">
         <v>70</v>
       </c>
-      <c r="G560" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G560" t="n">
+        <v>92.7</v>
       </c>
       <c r="H560" t="n">
         <v>76</v>
@@ -41011,10 +40817,8 @@
       <c r="F561" t="n">
         <v>70</v>
       </c>
-      <c r="G561" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G561" t="n">
+        <v>92.7</v>
       </c>
       <c r="H561" t="n">
         <v>76</v>
@@ -41085,10 +40889,8 @@
       <c r="F562" t="n">
         <v>70</v>
       </c>
-      <c r="G562" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G562" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H562" t="n">
         <v>76</v>
@@ -41159,10 +40961,8 @@
       <c r="F563" t="n">
         <v>70</v>
       </c>
-      <c r="G563" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G563" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H563" t="n">
         <v>76</v>
@@ -41233,10 +41033,8 @@
       <c r="F564" t="n">
         <v>70</v>
       </c>
-      <c r="G564" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G564" t="n">
+        <v>94.3</v>
       </c>
       <c r="H564" t="n">
         <v>68</v>
@@ -41307,10 +41105,8 @@
       <c r="F565" t="n">
         <v>70</v>
       </c>
-      <c r="G565" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G565" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H565" t="n">
         <v>76</v>
@@ -41381,10 +41177,8 @@
       <c r="F566" t="n">
         <v>70</v>
       </c>
-      <c r="G566" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G566" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H566" t="n">
         <v>76</v>
@@ -41455,10 +41249,8 @@
       <c r="F567" t="n">
         <v>70</v>
       </c>
-      <c r="G567" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G567" t="n">
+        <v>94.3</v>
       </c>
       <c r="H567" t="n">
         <v>68</v>
@@ -41529,10 +41321,8 @@
       <c r="F568" t="n">
         <v>70</v>
       </c>
-      <c r="G568" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G568" t="n">
+        <v>92.7</v>
       </c>
       <c r="H568" t="n">
         <v>76</v>
@@ -41603,10 +41393,8 @@
       <c r="F569" t="n">
         <v>70</v>
       </c>
-      <c r="G569" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G569" t="n">
+        <v>94.3</v>
       </c>
       <c r="H569" t="n">
         <v>76</v>
@@ -41677,10 +41465,8 @@
       <c r="F570" t="n">
         <v>70</v>
       </c>
-      <c r="G570" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G570" t="n">
+        <v>94.3</v>
       </c>
       <c r="H570" t="n">
         <v>68</v>
@@ -41751,10 +41537,8 @@
       <c r="F571" t="n">
         <v>70</v>
       </c>
-      <c r="G571" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G571" t="n">
+        <v>94.3</v>
       </c>
       <c r="H571" t="n">
         <v>76</v>
@@ -41825,10 +41609,8 @@
       <c r="F572" t="n">
         <v>70</v>
       </c>
-      <c r="G572" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G572" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H572" t="n">
         <v>76</v>
@@ -41899,10 +41681,8 @@
       <c r="F573" t="n">
         <v>70</v>
       </c>
-      <c r="G573" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G573" t="n">
+        <v>92.7</v>
       </c>
       <c r="H573" t="n">
         <v>76</v>
@@ -41973,10 +41753,8 @@
       <c r="F574" t="n">
         <v>70</v>
       </c>
-      <c r="G574" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G574" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H574" t="n">
         <v>76</v>
@@ -42047,10 +41825,8 @@
       <c r="F575" t="n">
         <v>70</v>
       </c>
-      <c r="G575" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G575" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H575" t="n">
         <v>76</v>
@@ -42121,10 +41897,8 @@
       <c r="F576" t="n">
         <v>70</v>
       </c>
-      <c r="G576" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G576" t="n">
+        <v>92.7</v>
       </c>
       <c r="H576" t="n">
         <v>76</v>
@@ -42195,10 +41969,8 @@
       <c r="F577" t="n">
         <v>70</v>
       </c>
-      <c r="G577" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G577" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H577" t="n">
         <v>76</v>
@@ -42269,10 +42041,8 @@
       <c r="F578" t="n">
         <v>70</v>
       </c>
-      <c r="G578" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G578" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H578" t="n">
         <v>76</v>
@@ -42343,10 +42113,8 @@
       <c r="F579" t="n">
         <v>70</v>
       </c>
-      <c r="G579" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G579" t="n">
+        <v>90.5</v>
       </c>
       <c r="H579" t="n">
         <v>76</v>
@@ -42417,10 +42185,8 @@
       <c r="F580" t="n">
         <v>70</v>
       </c>
-      <c r="G580" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G580" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H580" t="n">
         <v>76</v>
@@ -42491,10 +42257,8 @@
       <c r="F581" t="n">
         <v>70</v>
       </c>
-      <c r="G581" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G581" t="n">
+        <v>94.3</v>
       </c>
       <c r="H581" t="n">
         <v>68</v>
@@ -42565,10 +42329,8 @@
       <c r="F582" t="n">
         <v>70</v>
       </c>
-      <c r="G582" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G582" t="n">
+        <v>92.7</v>
       </c>
       <c r="H582" t="n">
         <v>76</v>
@@ -42639,10 +42401,8 @@
       <c r="F583" t="n">
         <v>70</v>
       </c>
-      <c r="G583" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G583" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H583" t="n">
         <v>76</v>
@@ -42713,10 +42473,8 @@
       <c r="F584" t="n">
         <v>70</v>
       </c>
-      <c r="G584" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G584" t="n">
+        <v>94.3</v>
       </c>
       <c r="H584" t="n">
         <v>68</v>
@@ -42787,10 +42545,8 @@
       <c r="F585" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="G585" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G585" t="n">
+        <v>94.3</v>
       </c>
       <c r="H585" t="n">
         <v>76</v>
@@ -42861,10 +42617,8 @@
       <c r="F586" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="G586" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G586" t="n">
+        <v>94.3</v>
       </c>
       <c r="H586" t="n">
         <v>76</v>
@@ -42935,10 +42689,8 @@
       <c r="F587" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="G587" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G587" t="n">
+        <v>94.3</v>
       </c>
       <c r="H587" t="n">
         <v>76</v>
@@ -43009,10 +42761,8 @@
       <c r="F588" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="G588" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G588" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H588" t="n">
         <v>70</v>
@@ -43083,10 +42833,8 @@
       <c r="F589" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="G589" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G589" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="H589" t="n">
         <v>76</v>
@@ -43157,10 +42905,8 @@
       <c r="F590" t="n">
         <v>70.8</v>
       </c>
-      <c r="G590" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G590" t="n">
+        <v>88.2</v>
       </c>
       <c r="H590" t="n">
         <v>68</v>
@@ -43231,10 +42977,8 @@
       <c r="F591" t="n">
         <v>70.8</v>
       </c>
-      <c r="G591" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G591" t="n">
+        <v>89.7</v>
       </c>
       <c r="H591" t="n">
         <v>68</v>
@@ -43305,10 +43049,8 @@
       <c r="F592" t="n">
         <v>70.8</v>
       </c>
-      <c r="G592" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G592" t="n">
+        <v>88.2</v>
       </c>
       <c r="H592" t="n">
         <v>68</v>
@@ -43379,10 +43121,8 @@
       <c r="F593" t="n">
         <v>70.8</v>
       </c>
-      <c r="G593" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G593" t="n">
+        <v>89.7</v>
       </c>
       <c r="H593" t="n">
         <v>76</v>
@@ -43453,10 +43193,8 @@
       <c r="F594" t="n">
         <v>70.8</v>
       </c>
-      <c r="G594" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G594" t="n">
+        <v>89.7</v>
       </c>
       <c r="H594" t="n">
         <v>68</v>
@@ -43527,10 +43265,8 @@
       <c r="F595" t="n">
         <v>70.8</v>
       </c>
-      <c r="G595" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G595" t="n">
+        <v>89.7</v>
       </c>
       <c r="H595" t="n">
         <v>76</v>
@@ -43601,10 +43337,8 @@
       <c r="F596" t="n">
         <v>70.8</v>
       </c>
-      <c r="G596" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G596" t="n">
+        <v>89.7</v>
       </c>
       <c r="H596" t="n">
         <v>76</v>
@@ -43675,10 +43409,8 @@
       <c r="F597" t="n">
         <v>70.8</v>
       </c>
-      <c r="G597" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G597" t="n">
+        <v>89.7</v>
       </c>
       <c r="H597" t="n">
         <v>76</v>
@@ -43749,10 +43481,8 @@
       <c r="F598" t="n">
         <v>70.8</v>
       </c>
-      <c r="G598" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G598" t="n">
+        <v>89.7</v>
       </c>
       <c r="H598" t="n">
         <v>68</v>
@@ -43823,10 +43553,8 @@
       <c r="F599" t="n">
         <v>71.2</v>
       </c>
-      <c r="G599" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G599" t="n">
+        <v>92.7</v>
       </c>
       <c r="H599" t="n">
         <v>68</v>
@@ -43897,10 +43625,8 @@
       <c r="F600" t="n">
         <v>71.2</v>
       </c>
-      <c r="G600" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G600" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H600" t="n">
         <v>70</v>
@@ -43971,10 +43697,8 @@
       <c r="F601" t="n">
         <v>71.2</v>
       </c>
-      <c r="G601" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G601" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H601" t="n">
         <v>70</v>
@@ -44045,10 +43769,8 @@
       <c r="F602" t="n">
         <v>71.2</v>
       </c>
-      <c r="G602" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G602" t="n">
+        <v>92.7</v>
       </c>
       <c r="H602" t="n">
         <v>76</v>
@@ -44119,10 +43841,8 @@
       <c r="F603" t="n">
         <v>71.2</v>
       </c>
-      <c r="G603" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G603" t="n">
+        <v>92.7</v>
       </c>
       <c r="H603" t="n">
         <v>68</v>
@@ -44193,10 +43913,8 @@
       <c r="F604" t="n">
         <v>71.2</v>
       </c>
-      <c r="G604" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G604" t="n">
+        <v>90.09999999999999</v>
       </c>
       <c r="H604" t="n">
         <v>70</v>
@@ -44267,10 +43985,8 @@
       <c r="F605" t="n">
         <v>71.2</v>
       </c>
-      <c r="G605" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G605" t="n">
+        <v>89.7</v>
       </c>
       <c r="H605" t="n">
         <v>76</v>
@@ -44341,10 +44057,8 @@
       <c r="F606" t="n">
         <v>71.2</v>
       </c>
-      <c r="G606" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G606" t="n">
+        <v>88.2</v>
       </c>
       <c r="H606" t="n">
         <v>76</v>
@@ -44415,10 +44129,8 @@
       <c r="F607" t="n">
         <v>71.2</v>
       </c>
-      <c r="G607" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G607" t="n">
+        <v>89.7</v>
       </c>
       <c r="H607" t="n">
         <v>76</v>
@@ -44489,10 +44201,8 @@
       <c r="F608" t="n">
         <v>71.5</v>
       </c>
-      <c r="G608" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G608" t="n">
+        <v>94.3</v>
       </c>
       <c r="H608" t="n">
         <v>76</v>
@@ -44563,10 +44273,8 @@
       <c r="F609" t="n">
         <v>71.5</v>
       </c>
-      <c r="G609" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G609" t="n">
+        <v>94.3</v>
       </c>
       <c r="H609" t="n">
         <v>76</v>
@@ -44637,10 +44345,8 @@
       <c r="F610" t="n">
         <v>71.5</v>
       </c>
-      <c r="G610" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G610" t="n">
+        <v>94.3</v>
       </c>
       <c r="H610" t="n">
         <v>76</v>
@@ -44711,10 +44417,8 @@
       <c r="F611" t="n">
         <v>71.5</v>
       </c>
-      <c r="G611" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G611" t="n">
+        <v>94.3</v>
       </c>
       <c r="H611" t="n">
         <v>76</v>
@@ -44785,10 +44489,8 @@
       <c r="F612" t="n">
         <v>71.5</v>
       </c>
-      <c r="G612" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G612" t="n">
+        <v>94.3</v>
       </c>
       <c r="H612" t="n">
         <v>76</v>
@@ -44859,10 +44561,8 @@
       <c r="F613" t="n">
         <v>71.5</v>
       </c>
-      <c r="G613" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G613" t="n">
+        <v>94.3</v>
       </c>
       <c r="H613" t="n">
         <v>76</v>
@@ -44933,10 +44633,8 @@
       <c r="F614" t="n">
         <v>71.5</v>
       </c>
-      <c r="G614" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G614" t="n">
+        <v>92.7</v>
       </c>
       <c r="H614" t="n">
         <v>76</v>
@@ -45007,10 +44705,8 @@
       <c r="F615" t="n">
         <v>71.5</v>
       </c>
-      <c r="G615" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G615" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H615" t="n">
         <v>76</v>
@@ -45081,10 +44777,8 @@
       <c r="F616" t="n">
         <v>71.5</v>
       </c>
-      <c r="G616" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G616" t="n">
+        <v>94.3</v>
       </c>
       <c r="H616" t="n">
         <v>76</v>
@@ -45155,10 +44849,8 @@
       <c r="F617" t="n">
         <v>71.5</v>
       </c>
-      <c r="G617" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G617" t="n">
+        <v>94.3</v>
       </c>
       <c r="H617" t="n">
         <v>76</v>
@@ -45229,10 +44921,8 @@
       <c r="F618" t="n">
         <v>71.5</v>
       </c>
-      <c r="G618" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G618" t="n">
+        <v>94.3</v>
       </c>
       <c r="H618" t="n">
         <v>76</v>
@@ -45303,10 +44993,8 @@
       <c r="F619" t="n">
         <v>71.5</v>
       </c>
-      <c r="G619" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G619" t="n">
+        <v>94.3</v>
       </c>
       <c r="H619" t="n">
         <v>76</v>
@@ -45377,10 +45065,8 @@
       <c r="F620" t="n">
         <v>71.5</v>
       </c>
-      <c r="G620" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G620" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="H620" t="n">
         <v>76</v>
@@ -45451,10 +45137,8 @@
       <c r="F621" t="n">
         <v>71.5</v>
       </c>
-      <c r="G621" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G621" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="H621" t="n">
         <v>76</v>
@@ -45525,10 +45209,8 @@
       <c r="F622" t="n">
         <v>71.5</v>
       </c>
-      <c r="G622" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G622" t="n">
+        <v>94.3</v>
       </c>
       <c r="H622" t="n">
         <v>76</v>
@@ -45599,10 +45281,8 @@
       <c r="F623" t="n">
         <v>71.5</v>
       </c>
-      <c r="G623" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G623" t="n">
+        <v>94.3</v>
       </c>
       <c r="H623" t="n">
         <v>76</v>
@@ -45673,10 +45353,8 @@
       <c r="F624" t="n">
         <v>71.5</v>
       </c>
-      <c r="G624" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G624" t="n">
+        <v>94.3</v>
       </c>
       <c r="H624" t="n">
         <v>76</v>
@@ -45747,10 +45425,8 @@
       <c r="F625" t="n">
         <v>71.5</v>
       </c>
-      <c r="G625" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G625" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="H625" t="n">
         <v>76</v>
@@ -45821,10 +45497,8 @@
       <c r="F626" t="n">
         <v>71.5</v>
       </c>
-      <c r="G626" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G626" t="n">
+        <v>94.3</v>
       </c>
       <c r="H626" t="n">
         <v>76</v>
@@ -45895,10 +45569,8 @@
       <c r="F627" t="n">
         <v>71.5</v>
       </c>
-      <c r="G627" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G627" t="n">
+        <v>94.3</v>
       </c>
       <c r="H627" t="n">
         <v>76</v>
@@ -45969,10 +45641,8 @@
       <c r="F628" t="n">
         <v>71.5</v>
       </c>
-      <c r="G628" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G628" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="H628" t="n">
         <v>76</v>
@@ -46043,10 +45713,8 @@
       <c r="F629" t="n">
         <v>71.5</v>
       </c>
-      <c r="G629" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G629" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="H629" t="n">
         <v>76</v>
@@ -46117,10 +45785,8 @@
       <c r="F630" t="n">
         <v>71.5</v>
       </c>
-      <c r="G630" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G630" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="H630" t="n">
         <v>76</v>
@@ -46191,10 +45857,8 @@
       <c r="F631" t="n">
         <v>71.5</v>
       </c>
-      <c r="G631" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G631" t="n">
+        <v>94.3</v>
       </c>
       <c r="H631" t="n">
         <v>76</v>
@@ -46265,10 +45929,8 @@
       <c r="F632" t="n">
         <v>72.3</v>
       </c>
-      <c r="G632" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G632" t="n">
+        <v>92.7</v>
       </c>
       <c r="H632" t="n">
         <v>76</v>
@@ -46339,10 +46001,8 @@
       <c r="F633" t="n">
         <v>72.3</v>
       </c>
-      <c r="G633" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G633" t="n">
+        <v>94.3</v>
       </c>
       <c r="H633" t="n">
         <v>76</v>
@@ -46413,10 +46073,8 @@
       <c r="F634" t="n">
         <v>72.3</v>
       </c>
-      <c r="G634" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G634" t="n">
+        <v>89.7</v>
       </c>
       <c r="H634" t="n">
         <v>68</v>
@@ -46487,10 +46145,8 @@
       <c r="F635" t="n">
         <v>72.3</v>
       </c>
-      <c r="G635" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G635" t="n">
+        <v>92.7</v>
       </c>
       <c r="H635" t="n">
         <v>68</v>
@@ -46561,10 +46217,8 @@
       <c r="F636" t="n">
         <v>72.3</v>
       </c>
-      <c r="G636" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G636" t="n">
+        <v>88.2</v>
       </c>
       <c r="H636" t="n">
         <v>76</v>
@@ -46635,10 +46289,8 @@
       <c r="F637" t="n">
         <v>72.3</v>
       </c>
-      <c r="G637" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G637" t="n">
+        <v>92.7</v>
       </c>
       <c r="H637" t="n">
         <v>76</v>
@@ -46709,10 +46361,8 @@
       <c r="F638" t="n">
         <v>72.3</v>
       </c>
-      <c r="G638" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G638" t="n">
+        <v>92.7</v>
       </c>
       <c r="H638" t="n">
         <v>68</v>
@@ -46783,10 +46433,8 @@
       <c r="F639" t="n">
         <v>72.3</v>
       </c>
-      <c r="G639" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G639" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H639" t="n">
         <v>76</v>
@@ -46857,10 +46505,8 @@
       <c r="F640" t="n">
         <v>72.3</v>
       </c>
-      <c r="G640" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G640" t="n">
+        <v>88.5</v>
       </c>
       <c r="H640" t="n">
         <v>76</v>
@@ -46931,10 +46577,8 @@
       <c r="F641" t="n">
         <v>72.3</v>
       </c>
-      <c r="G641" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G641" t="n">
+        <v>89.7</v>
       </c>
       <c r="H641" t="n">
         <v>68</v>
@@ -47005,10 +46649,8 @@
       <c r="F642" t="n">
         <v>72.3</v>
       </c>
-      <c r="G642" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G642" t="n">
+        <v>92.7</v>
       </c>
       <c r="H642" t="n">
         <v>76</v>
@@ -47079,10 +46721,8 @@
       <c r="F643" t="n">
         <v>72.3</v>
       </c>
-      <c r="G643" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G643" t="n">
+        <v>89.7</v>
       </c>
       <c r="H643" t="n">
         <v>76</v>
@@ -47153,10 +46793,8 @@
       <c r="F644" t="n">
         <v>72.3</v>
       </c>
-      <c r="G644" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G644" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H644" t="n">
         <v>76</v>
@@ -47227,10 +46865,8 @@
       <c r="F645" t="n">
         <v>72.3</v>
       </c>
-      <c r="G645" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G645" t="n">
+        <v>88.5</v>
       </c>
       <c r="H645" t="n">
         <v>76</v>
@@ -47301,10 +46937,8 @@
       <c r="F646" t="n">
         <v>72.3</v>
       </c>
-      <c r="G646" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G646" t="n">
+        <v>92.7</v>
       </c>
       <c r="H646" t="n">
         <v>76</v>
@@ -47375,10 +47009,8 @@
       <c r="F647" t="n">
         <v>72.3</v>
       </c>
-      <c r="G647" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G647" t="n">
+        <v>92.7</v>
       </c>
       <c r="H647" t="n">
         <v>76</v>
@@ -47449,10 +47081,8 @@
       <c r="F648" t="n">
         <v>72.3</v>
       </c>
-      <c r="G648" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G648" t="n">
+        <v>88.2</v>
       </c>
       <c r="H648" t="n">
         <v>76</v>
@@ -47523,10 +47153,8 @@
       <c r="F649" t="n">
         <v>72.3</v>
       </c>
-      <c r="G649" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G649" t="n">
+        <v>89.7</v>
       </c>
       <c r="H649" t="n">
         <v>76</v>
@@ -47597,10 +47225,8 @@
       <c r="F650" t="n">
         <v>72.3</v>
       </c>
-      <c r="G650" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G650" t="n">
+        <v>89.7</v>
       </c>
       <c r="H650" t="n">
         <v>76</v>
@@ -47671,10 +47297,8 @@
       <c r="F651" t="n">
         <v>72.3</v>
       </c>
-      <c r="G651" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G651" t="n">
+        <v>88.5</v>
       </c>
       <c r="H651" t="n">
         <v>76</v>
@@ -47745,10 +47369,8 @@
       <c r="F652" t="n">
         <v>72.3</v>
       </c>
-      <c r="G652" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G652" t="n">
+        <v>89.7</v>
       </c>
       <c r="H652" t="n">
         <v>76</v>
@@ -47819,10 +47441,8 @@
       <c r="F653" t="n">
         <v>72.3</v>
       </c>
-      <c r="G653" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G653" t="n">
+        <v>89.7</v>
       </c>
       <c r="H653" t="n">
         <v>76</v>
@@ -47893,10 +47513,8 @@
       <c r="F654" t="n">
         <v>72.3</v>
       </c>
-      <c r="G654" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G654" t="n">
+        <v>92.7</v>
       </c>
       <c r="H654" t="n">
         <v>76</v>
@@ -47967,10 +47585,8 @@
       <c r="F655" t="n">
         <v>72.3</v>
       </c>
-      <c r="G655" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G655" t="n">
+        <v>88.2</v>
       </c>
       <c r="H655" t="n">
         <v>76</v>
@@ -48041,10 +47657,8 @@
       <c r="F656" t="n">
         <v>72.3</v>
       </c>
-      <c r="G656" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G656" t="n">
+        <v>88.2</v>
       </c>
       <c r="H656" t="n">
         <v>76</v>
@@ -48115,10 +47729,8 @@
       <c r="F657" t="n">
         <v>72.3</v>
       </c>
-      <c r="G657" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G657" t="n">
+        <v>92.7</v>
       </c>
       <c r="H657" t="n">
         <v>68</v>
@@ -48189,10 +47801,8 @@
       <c r="F658" t="n">
         <v>72.3</v>
       </c>
-      <c r="G658" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G658" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H658" t="n">
         <v>76</v>
@@ -48263,10 +47873,8 @@
       <c r="F659" t="n">
         <v>72.3</v>
       </c>
-      <c r="G659" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G659" t="n">
+        <v>92.7</v>
       </c>
       <c r="H659" t="n">
         <v>76</v>
@@ -48337,10 +47945,8 @@
       <c r="F660" t="n">
         <v>72.3</v>
       </c>
-      <c r="G660" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G660" t="n">
+        <v>88.2</v>
       </c>
       <c r="H660" t="n">
         <v>76</v>
@@ -48411,10 +48017,8 @@
       <c r="F661" t="n">
         <v>72.3</v>
       </c>
-      <c r="G661" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G661" t="n">
+        <v>88.2</v>
       </c>
       <c r="H661" t="n">
         <v>76</v>
@@ -48485,10 +48089,8 @@
       <c r="F662" t="n">
         <v>72.3</v>
       </c>
-      <c r="G662" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G662" t="n">
+        <v>92.7</v>
       </c>
       <c r="H662" t="n">
         <v>76</v>
@@ -48559,10 +48161,8 @@
       <c r="F663" t="n">
         <v>72.3</v>
       </c>
-      <c r="G663" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G663" t="n">
+        <v>92.7</v>
       </c>
       <c r="H663" t="n">
         <v>68</v>
@@ -48633,10 +48233,8 @@
       <c r="F664" t="n">
         <v>72.3</v>
       </c>
-      <c r="G664" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G664" t="n">
+        <v>89.7</v>
       </c>
       <c r="H664" t="n">
         <v>76</v>
@@ -48707,10 +48305,8 @@
       <c r="F665" t="n">
         <v>72.3</v>
       </c>
-      <c r="G665" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G665" t="n">
+        <v>91.2</v>
       </c>
       <c r="H665" t="n">
         <v>68</v>
@@ -48781,10 +48377,8 @@
       <c r="F666" t="n">
         <v>72.3</v>
       </c>
-      <c r="G666" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G666" t="n">
+        <v>89.7</v>
       </c>
       <c r="H666" t="n">
         <v>76</v>
@@ -48855,10 +48449,8 @@
       <c r="F667" t="n">
         <v>72.3</v>
       </c>
-      <c r="G667" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G667" t="n">
+        <v>92.7</v>
       </c>
       <c r="H667" t="n">
         <v>68</v>
@@ -48929,10 +48521,8 @@
       <c r="F668" t="n">
         <v>72.7</v>
       </c>
-      <c r="G668" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G668" t="n">
+        <v>92.7</v>
       </c>
       <c r="H668" t="n">
         <v>76</v>
@@ -49003,10 +48593,8 @@
       <c r="F669" t="n">
         <v>72.7</v>
       </c>
-      <c r="G669" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G669" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H669" t="n">
         <v>70</v>
@@ -49077,10 +48665,8 @@
       <c r="F670" t="n">
         <v>72.7</v>
       </c>
-      <c r="G670" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G670" t="n">
+        <v>92.7</v>
       </c>
       <c r="H670" t="n">
         <v>76</v>
@@ -49151,10 +48737,8 @@
       <c r="F671" t="n">
         <v>72.7</v>
       </c>
-      <c r="G671" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G671" t="n">
+        <v>92.7</v>
       </c>
       <c r="H671" t="n">
         <v>76</v>
@@ -49225,10 +48809,8 @@
       <c r="F672" t="n">
         <v>72.7</v>
       </c>
-      <c r="G672" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G672" t="n">
+        <v>92.7</v>
       </c>
       <c r="H672" t="n">
         <v>76</v>
@@ -49299,10 +48881,8 @@
       <c r="F673" t="n">
         <v>72.7</v>
       </c>
-      <c r="G673" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G673" t="n">
+        <v>92.7</v>
       </c>
       <c r="H673" t="n">
         <v>76</v>
@@ -49373,10 +48953,8 @@
       <c r="F674" t="n">
         <v>72.7</v>
       </c>
-      <c r="G674" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G674" t="n">
+        <v>92.7</v>
       </c>
       <c r="H674" t="n">
         <v>76</v>
@@ -49447,10 +49025,8 @@
       <c r="F675" t="n">
         <v>72.7</v>
       </c>
-      <c r="G675" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G675" t="n">
+        <v>92.7</v>
       </c>
       <c r="H675" t="n">
         <v>76</v>
@@ -49521,10 +49097,8 @@
       <c r="F676" t="n">
         <v>72.7</v>
       </c>
-      <c r="G676" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G676" t="n">
+        <v>92.7</v>
       </c>
       <c r="H676" t="n">
         <v>76</v>
@@ -49595,10 +49169,8 @@
       <c r="F677" t="n">
         <v>72.7</v>
       </c>
-      <c r="G677" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G677" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H677" t="n">
         <v>70</v>
@@ -49669,10 +49241,8 @@
       <c r="F678" t="n">
         <v>72.7</v>
       </c>
-      <c r="G678" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G678" t="n">
+        <v>92.7</v>
       </c>
       <c r="H678" t="n">
         <v>76</v>
@@ -49743,10 +49313,8 @@
       <c r="F679" t="n">
         <v>72.7</v>
       </c>
-      <c r="G679" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G679" t="n">
+        <v>94.3</v>
       </c>
       <c r="H679" t="n">
         <v>76</v>
@@ -49817,10 +49385,8 @@
       <c r="F680" t="n">
         <v>72.7</v>
       </c>
-      <c r="G680" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G680" t="n">
+        <v>92.7</v>
       </c>
       <c r="H680" t="n">
         <v>76</v>
@@ -49891,10 +49457,8 @@
       <c r="F681" t="n">
         <v>72.7</v>
       </c>
-      <c r="G681" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G681" t="n">
+        <v>92.7</v>
       </c>
       <c r="H681" t="n">
         <v>76</v>
@@ -49965,10 +49529,8 @@
       <c r="F682" t="n">
         <v>72.7</v>
       </c>
-      <c r="G682" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G682" t="n">
+        <v>92.7</v>
       </c>
       <c r="H682" t="n">
         <v>76</v>
@@ -50039,10 +49601,8 @@
       <c r="F683" t="n">
         <v>72.7</v>
       </c>
-      <c r="G683" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G683" t="n">
+        <v>92.7</v>
       </c>
       <c r="H683" t="n">
         <v>76</v>
@@ -50113,10 +49673,8 @@
       <c r="F684" t="n">
         <v>72.7</v>
       </c>
-      <c r="G684" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G684" t="n">
+        <v>92.7</v>
       </c>
       <c r="H684" t="n">
         <v>76</v>
@@ -50187,10 +49745,8 @@
       <c r="F685" t="n">
         <v>72.7</v>
       </c>
-      <c r="G685" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G685" t="n">
+        <v>89.7</v>
       </c>
       <c r="H685" t="n">
         <v>76</v>
@@ -50261,10 +49817,8 @@
       <c r="F686" t="n">
         <v>72.7</v>
       </c>
-      <c r="G686" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G686" t="n">
+        <v>92.7</v>
       </c>
       <c r="H686" t="n">
         <v>76</v>
@@ -50335,10 +49889,8 @@
       <c r="F687" t="n">
         <v>72.7</v>
       </c>
-      <c r="G687" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G687" t="n">
+        <v>92.7</v>
       </c>
       <c r="H687" t="n">
         <v>76</v>
@@ -50409,10 +49961,8 @@
       <c r="F688" t="n">
         <v>72.7</v>
       </c>
-      <c r="G688" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G688" t="n">
+        <v>92.7</v>
       </c>
       <c r="H688" t="n">
         <v>76</v>
@@ -50483,10 +50033,8 @@
       <c r="F689" t="n">
         <v>72.7</v>
       </c>
-      <c r="G689" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G689" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H689" t="n">
         <v>70</v>
@@ -50557,10 +50105,8 @@
       <c r="F690" t="n">
         <v>72.7</v>
       </c>
-      <c r="G690" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G690" t="n">
+        <v>92.7</v>
       </c>
       <c r="H690" t="n">
         <v>76</v>
@@ -50631,10 +50177,8 @@
       <c r="F691" t="n">
         <v>73.09999999999999</v>
       </c>
-      <c r="G691" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G691" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H691" t="n">
         <v>70</v>
@@ -50705,10 +50249,8 @@
       <c r="F692" t="n">
         <v>73.8</v>
       </c>
-      <c r="G692" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G692" t="n">
+        <v>89.7</v>
       </c>
       <c r="H692" t="n">
         <v>76</v>
@@ -50779,10 +50321,8 @@
       <c r="F693" t="n">
         <v>73.8</v>
       </c>
-      <c r="G693" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G693" t="n">
+        <v>92.7</v>
       </c>
       <c r="H693" t="n">
         <v>76</v>
@@ -50853,10 +50393,8 @@
       <c r="F694" t="n">
         <v>73.8</v>
       </c>
-      <c r="G694" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G694" t="n">
+        <v>92.7</v>
       </c>
       <c r="H694" t="n">
         <v>76</v>
@@ -50927,10 +50465,8 @@
       <c r="F695" t="n">
         <v>73.8</v>
       </c>
-      <c r="G695" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G695" t="n">
+        <v>94.3</v>
       </c>
       <c r="H695" t="n">
         <v>76</v>
@@ -51001,10 +50537,8 @@
       <c r="F696" t="n">
         <v>73.8</v>
       </c>
-      <c r="G696" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G696" t="n">
+        <v>89.7</v>
       </c>
       <c r="H696" t="n">
         <v>76</v>
@@ -51075,10 +50609,8 @@
       <c r="F697" t="n">
         <v>73.8</v>
       </c>
-      <c r="G697" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G697" t="n">
+        <v>92.7</v>
       </c>
       <c r="H697" t="n">
         <v>76</v>
@@ -51149,10 +50681,8 @@
       <c r="F698" t="n">
         <v>73.8</v>
       </c>
-      <c r="G698" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G698" t="n">
+        <v>89.7</v>
       </c>
       <c r="H698" t="n">
         <v>76</v>
@@ -51223,10 +50753,8 @@
       <c r="F699" t="n">
         <v>73.8</v>
       </c>
-      <c r="G699" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G699" t="n">
+        <v>92.7</v>
       </c>
       <c r="H699" t="n">
         <v>76</v>
@@ -51297,10 +50825,8 @@
       <c r="F700" t="n">
         <v>73.8</v>
       </c>
-      <c r="G700" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G700" t="n">
+        <v>92.7</v>
       </c>
       <c r="H700" t="n">
         <v>76</v>
@@ -51371,10 +50897,8 @@
       <c r="F701" t="n">
         <v>73.8</v>
       </c>
-      <c r="G701" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G701" t="n">
+        <v>92.7</v>
       </c>
       <c r="H701" t="n">
         <v>76</v>
@@ -51445,10 +50969,8 @@
       <c r="F702" t="n">
         <v>73.8</v>
       </c>
-      <c r="G702" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G702" t="n">
+        <v>92.7</v>
       </c>
       <c r="H702" t="n">
         <v>76</v>
@@ -51519,10 +51041,8 @@
       <c r="F703" t="n">
         <v>73.8</v>
       </c>
-      <c r="G703" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G703" t="n">
+        <v>92.7</v>
       </c>
       <c r="H703" t="n">
         <v>76</v>
@@ -51593,10 +51113,8 @@
       <c r="F704" t="n">
         <v>73.8</v>
       </c>
-      <c r="G704" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G704" t="n">
+        <v>92.7</v>
       </c>
       <c r="H704" t="n">
         <v>76</v>
@@ -51667,10 +51185,8 @@
       <c r="F705" t="n">
         <v>73.8</v>
       </c>
-      <c r="G705" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G705" t="n">
+        <v>92.7</v>
       </c>
       <c r="H705" t="n">
         <v>76</v>
@@ -51741,10 +51257,8 @@
       <c r="F706" t="n">
         <v>73.8</v>
       </c>
-      <c r="G706" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G706" t="n">
+        <v>92.7</v>
       </c>
       <c r="H706" t="n">
         <v>76</v>
@@ -51815,10 +51329,8 @@
       <c r="F707" t="n">
         <v>73.8</v>
       </c>
-      <c r="G707" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G707" t="n">
+        <v>92.7</v>
       </c>
       <c r="H707" t="n">
         <v>76</v>
@@ -51889,10 +51401,8 @@
       <c r="F708" t="n">
         <v>73.8</v>
       </c>
-      <c r="G708" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G708" t="n">
+        <v>92.7</v>
       </c>
       <c r="H708" t="n">
         <v>76</v>
@@ -51963,10 +51473,8 @@
       <c r="F709" t="n">
         <v>73.8</v>
       </c>
-      <c r="G709" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G709" t="n">
+        <v>92.7</v>
       </c>
       <c r="H709" t="n">
         <v>76</v>
@@ -52037,10 +51545,8 @@
       <c r="F710" t="n">
         <v>73.8</v>
       </c>
-      <c r="G710" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G710" t="n">
+        <v>92.7</v>
       </c>
       <c r="H710" t="n">
         <v>76</v>
@@ -52111,10 +51617,8 @@
       <c r="F711" t="n">
         <v>73.8</v>
       </c>
-      <c r="G711" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G711" t="n">
+        <v>92.7</v>
       </c>
       <c r="H711" t="n">
         <v>76</v>
@@ -52185,10 +51689,8 @@
       <c r="F712" t="n">
         <v>73.8</v>
       </c>
-      <c r="G712" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G712" t="n">
+        <v>92.7</v>
       </c>
       <c r="H712" t="n">
         <v>76</v>
@@ -52259,10 +51761,8 @@
       <c r="F713" t="n">
         <v>73.8</v>
       </c>
-      <c r="G713" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G713" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H713" t="n">
         <v>76</v>
@@ -52333,10 +51833,8 @@
       <c r="F714" t="n">
         <v>73.8</v>
       </c>
-      <c r="G714" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G714" t="n">
+        <v>92.7</v>
       </c>
       <c r="H714" t="n">
         <v>76</v>
@@ -52407,10 +51905,8 @@
       <c r="F715" t="n">
         <v>73.8</v>
       </c>
-      <c r="G715" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G715" t="n">
+        <v>92.7</v>
       </c>
       <c r="H715" t="n">
         <v>76</v>
@@ -52481,10 +51977,8 @@
       <c r="F716" t="n">
         <v>73.8</v>
       </c>
-      <c r="G716" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G716" t="n">
+        <v>92.7</v>
       </c>
       <c r="H716" t="n">
         <v>76</v>
@@ -52555,10 +52049,8 @@
       <c r="F717" t="n">
         <v>73.8</v>
       </c>
-      <c r="G717" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G717" t="n">
+        <v>92.7</v>
       </c>
       <c r="H717" t="n">
         <v>76</v>
@@ -52629,10 +52121,8 @@
       <c r="F718" t="n">
         <v>73.8</v>
       </c>
-      <c r="G718" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G718" t="n">
+        <v>89.7</v>
       </c>
       <c r="H718" t="n">
         <v>76</v>
@@ -52703,10 +52193,8 @@
       <c r="F719" t="n">
         <v>73.8</v>
       </c>
-      <c r="G719" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G719" t="n">
+        <v>92.7</v>
       </c>
       <c r="H719" t="n">
         <v>76</v>
@@ -52777,10 +52265,8 @@
       <c r="F720" t="n">
         <v>73.8</v>
       </c>
-      <c r="G720" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G720" t="n">
+        <v>92.7</v>
       </c>
       <c r="H720" t="n">
         <v>76</v>
@@ -52851,10 +52337,8 @@
       <c r="F721" t="n">
         <v>73.8</v>
       </c>
-      <c r="G721" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G721" t="n">
+        <v>92.7</v>
       </c>
       <c r="H721" t="n">
         <v>76</v>
@@ -52925,10 +52409,8 @@
       <c r="F722" t="n">
         <v>73.8</v>
       </c>
-      <c r="G722" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G722" t="n">
+        <v>92.7</v>
       </c>
       <c r="H722" t="n">
         <v>76</v>
@@ -52999,10 +52481,8 @@
       <c r="F723" t="n">
         <v>73.8</v>
       </c>
-      <c r="G723" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G723" t="n">
+        <v>92.7</v>
       </c>
       <c r="H723" t="n">
         <v>76</v>
@@ -53073,10 +52553,8 @@
       <c r="F724" t="n">
         <v>73.8</v>
       </c>
-      <c r="G724" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G724" t="n">
+        <v>92.7</v>
       </c>
       <c r="H724" t="n">
         <v>76</v>
@@ -53147,10 +52625,8 @@
       <c r="F725" t="n">
         <v>73.8</v>
       </c>
-      <c r="G725" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G725" t="n">
+        <v>92.7</v>
       </c>
       <c r="H725" t="n">
         <v>76</v>
@@ -53221,10 +52697,8 @@
       <c r="F726" t="n">
         <v>73.8</v>
       </c>
-      <c r="G726" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G726" t="n">
+        <v>92.7</v>
       </c>
       <c r="H726" t="n">
         <v>76</v>
@@ -53295,10 +52769,8 @@
       <c r="F727" t="n">
         <v>73.8</v>
       </c>
-      <c r="G727" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G727" t="n">
+        <v>92.7</v>
       </c>
       <c r="H727" t="n">
         <v>76</v>
@@ -53369,10 +52841,8 @@
       <c r="F728" t="n">
         <v>73.8</v>
       </c>
-      <c r="G728" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G728" t="n">
+        <v>92.7</v>
       </c>
       <c r="H728" t="n">
         <v>76</v>
@@ -53443,10 +52913,8 @@
       <c r="F729" t="n">
         <v>73.8</v>
       </c>
-      <c r="G729" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G729" t="n">
+        <v>92.7</v>
       </c>
       <c r="H729" t="n">
         <v>68</v>
@@ -53517,10 +52985,8 @@
       <c r="F730" t="n">
         <v>73.8</v>
       </c>
-      <c r="G730" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G730" t="n">
+        <v>89.7</v>
       </c>
       <c r="H730" t="n">
         <v>76</v>
@@ -53591,10 +53057,8 @@
       <c r="F731" t="n">
         <v>73.8</v>
       </c>
-      <c r="G731" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G731" t="n">
+        <v>92.7</v>
       </c>
       <c r="H731" t="n">
         <v>76</v>
@@ -53665,10 +53129,8 @@
       <c r="F732" t="n">
         <v>73.8</v>
       </c>
-      <c r="G732" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G732" t="n">
+        <v>92.7</v>
       </c>
       <c r="H732" t="n">
         <v>76</v>
@@ -53739,10 +53201,8 @@
       <c r="F733" t="n">
         <v>73.8</v>
       </c>
-      <c r="G733" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G733" t="n">
+        <v>92.7</v>
       </c>
       <c r="H733" t="n">
         <v>76</v>
@@ -53813,10 +53273,8 @@
       <c r="F734" t="n">
         <v>73.8</v>
       </c>
-      <c r="G734" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G734" t="n">
+        <v>92.7</v>
       </c>
       <c r="H734" t="n">
         <v>76</v>
@@ -53887,10 +53345,8 @@
       <c r="F735" t="n">
         <v>73.8</v>
       </c>
-      <c r="G735" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G735" t="n">
+        <v>89.7</v>
       </c>
       <c r="H735" t="n">
         <v>76</v>
@@ -53961,10 +53417,8 @@
       <c r="F736" t="n">
         <v>73.8</v>
       </c>
-      <c r="G736" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G736" t="n">
+        <v>89.7</v>
       </c>
       <c r="H736" t="n">
         <v>76</v>
@@ -54035,10 +53489,8 @@
       <c r="F737" t="n">
         <v>73.8</v>
       </c>
-      <c r="G737" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G737" t="n">
+        <v>92.7</v>
       </c>
       <c r="H737" t="n">
         <v>76</v>
@@ -54109,10 +53561,8 @@
       <c r="F738" t="n">
         <v>73.8</v>
       </c>
-      <c r="G738" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G738" t="n">
+        <v>92.7</v>
       </c>
       <c r="H738" t="n">
         <v>76</v>
@@ -54183,10 +53633,8 @@
       <c r="F739" t="n">
         <v>73.8</v>
       </c>
-      <c r="G739" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G739" t="n">
+        <v>92.7</v>
       </c>
       <c r="H739" t="n">
         <v>76</v>
@@ -54257,10 +53705,8 @@
       <c r="F740" t="n">
         <v>73.8</v>
       </c>
-      <c r="G740" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G740" t="n">
+        <v>89.7</v>
       </c>
       <c r="H740" t="n">
         <v>76</v>
@@ -54331,10 +53777,8 @@
       <c r="F741" t="n">
         <v>73.8</v>
       </c>
-      <c r="G741" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G741" t="n">
+        <v>89.7</v>
       </c>
       <c r="H741" t="n">
         <v>76</v>
@@ -54405,10 +53849,8 @@
       <c r="F742" t="n">
         <v>73.8</v>
       </c>
-      <c r="G742" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G742" t="n">
+        <v>92.7</v>
       </c>
       <c r="H742" t="n">
         <v>76</v>
@@ -54479,10 +53921,8 @@
       <c r="F743" t="n">
         <v>73.8</v>
       </c>
-      <c r="G743" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G743" t="n">
+        <v>92.7</v>
       </c>
       <c r="H743" t="n">
         <v>76</v>
@@ -54553,10 +53993,8 @@
       <c r="F744" t="n">
         <v>73.8</v>
       </c>
-      <c r="G744" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G744" t="n">
+        <v>92.7</v>
       </c>
       <c r="H744" t="n">
         <v>76</v>
@@ -54627,10 +54065,8 @@
       <c r="F745" t="n">
         <v>73.8</v>
       </c>
-      <c r="G745" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G745" t="n">
+        <v>92.7</v>
       </c>
       <c r="H745" t="n">
         <v>76</v>
@@ -54701,10 +54137,8 @@
       <c r="F746" t="n">
         <v>73.8</v>
       </c>
-      <c r="G746" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G746" t="n">
+        <v>92.7</v>
       </c>
       <c r="H746" t="n">
         <v>76</v>
@@ -54775,10 +54209,8 @@
       <c r="F747" t="n">
         <v>73.8</v>
       </c>
-      <c r="G747" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G747" t="n">
+        <v>92.7</v>
       </c>
       <c r="H747" t="n">
         <v>76</v>
@@ -54849,10 +54281,8 @@
       <c r="F748" t="n">
         <v>73.8</v>
       </c>
-      <c r="G748" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G748" t="n">
+        <v>92.7</v>
       </c>
       <c r="H748" t="n">
         <v>76</v>
@@ -54923,10 +54353,8 @@
       <c r="F749" t="n">
         <v>73.8</v>
       </c>
-      <c r="G749" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G749" t="n">
+        <v>92.7</v>
       </c>
       <c r="H749" t="n">
         <v>76</v>
@@ -54997,10 +54425,8 @@
       <c r="F750" t="n">
         <v>73.8</v>
       </c>
-      <c r="G750" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G750" t="n">
+        <v>91.2</v>
       </c>
       <c r="H750" t="n">
         <v>68</v>
@@ -55071,10 +54497,8 @@
       <c r="F751" t="n">
         <v>73.8</v>
       </c>
-      <c r="G751" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G751" t="n">
+        <v>92.7</v>
       </c>
       <c r="H751" t="n">
         <v>76</v>
@@ -55145,10 +54569,8 @@
       <c r="F752" t="n">
         <v>73.8</v>
       </c>
-      <c r="G752" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G752" t="n">
+        <v>92.7</v>
       </c>
       <c r="H752" t="n">
         <v>76</v>
@@ -55219,10 +54641,8 @@
       <c r="F753" t="n">
         <v>73.8</v>
       </c>
-      <c r="G753" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G753" t="n">
+        <v>92.7</v>
       </c>
       <c r="H753" t="n">
         <v>76</v>
@@ -55293,10 +54713,8 @@
       <c r="F754" t="n">
         <v>73.8</v>
       </c>
-      <c r="G754" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G754" t="n">
+        <v>92.7</v>
       </c>
       <c r="H754" t="n">
         <v>76</v>
@@ -55367,10 +54785,8 @@
       <c r="F755" t="n">
         <v>73.8</v>
       </c>
-      <c r="G755" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G755" t="n">
+        <v>91.2</v>
       </c>
       <c r="H755" t="n">
         <v>76</v>
@@ -55441,10 +54857,8 @@
       <c r="F756" t="n">
         <v>73.8</v>
       </c>
-      <c r="G756" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G756" t="n">
+        <v>92.7</v>
       </c>
       <c r="H756" t="n">
         <v>76</v>
@@ -55515,10 +54929,8 @@
       <c r="F757" t="n">
         <v>73.8</v>
       </c>
-      <c r="G757" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G757" t="n">
+        <v>89.7</v>
       </c>
       <c r="H757" t="n">
         <v>76</v>
@@ -55589,10 +55001,8 @@
       <c r="F758" t="n">
         <v>73.8</v>
       </c>
-      <c r="G758" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G758" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H758" t="n">
         <v>76</v>
@@ -55663,10 +55073,8 @@
       <c r="F759" t="n">
         <v>73.8</v>
       </c>
-      <c r="G759" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G759" t="n">
+        <v>92.7</v>
       </c>
       <c r="H759" t="n">
         <v>76</v>
@@ -55737,10 +55145,8 @@
       <c r="F760" t="n">
         <v>73.8</v>
       </c>
-      <c r="G760" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G760" t="n">
+        <v>92.7</v>
       </c>
       <c r="H760" t="n">
         <v>76</v>
@@ -55811,10 +55217,8 @@
       <c r="F761" t="n">
         <v>73.8</v>
       </c>
-      <c r="G761" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G761" t="n">
+        <v>92.7</v>
       </c>
       <c r="H761" t="n">
         <v>76</v>
@@ -55885,10 +55289,8 @@
       <c r="F762" t="n">
         <v>73.8</v>
       </c>
-      <c r="G762" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G762" t="n">
+        <v>92.7</v>
       </c>
       <c r="H762" t="n">
         <v>76</v>
@@ -55959,10 +55361,8 @@
       <c r="F763" t="n">
         <v>73.8</v>
       </c>
-      <c r="G763" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G763" t="n">
+        <v>91.2</v>
       </c>
       <c r="H763" t="n">
         <v>76</v>
@@ -56033,10 +55433,8 @@
       <c r="F764" t="n">
         <v>73.8</v>
       </c>
-      <c r="G764" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G764" t="n">
+        <v>92.7</v>
       </c>
       <c r="H764" t="n">
         <v>76</v>
@@ -56107,10 +55505,8 @@
       <c r="F765" t="n">
         <v>73.8</v>
       </c>
-      <c r="G765" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G765" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H765" t="n">
         <v>76</v>
@@ -56181,10 +55577,8 @@
       <c r="F766" t="n">
         <v>73.8</v>
       </c>
-      <c r="G766" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G766" t="n">
+        <v>92.7</v>
       </c>
       <c r="H766" t="n">
         <v>76</v>
@@ -56255,10 +55649,8 @@
       <c r="F767" t="n">
         <v>73.8</v>
       </c>
-      <c r="G767" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G767" t="n">
+        <v>89.7</v>
       </c>
       <c r="H767" t="n">
         <v>76</v>
@@ -56329,10 +55721,8 @@
       <c r="F768" t="n">
         <v>73.8</v>
       </c>
-      <c r="G768" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G768" t="n">
+        <v>94.3</v>
       </c>
       <c r="H768" t="n">
         <v>76</v>
@@ -56403,10 +55793,8 @@
       <c r="F769" t="n">
         <v>73.8</v>
       </c>
-      <c r="G769" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G769" t="n">
+        <v>89.7</v>
       </c>
       <c r="H769" t="n">
         <v>76</v>
@@ -56477,10 +55865,8 @@
       <c r="F770" t="n">
         <v>73.8</v>
       </c>
-      <c r="G770" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G770" t="n">
+        <v>92.7</v>
       </c>
       <c r="H770" t="n">
         <v>76</v>
@@ -56551,10 +55937,8 @@
       <c r="F771" t="n">
         <v>74.2</v>
       </c>
-      <c r="G771" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G771" t="n">
+        <v>91.2</v>
       </c>
       <c r="H771" t="n">
         <v>76</v>
@@ -56625,10 +56009,8 @@
       <c r="F772" t="n">
         <v>74.2</v>
       </c>
-      <c r="G772" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G772" t="n">
+        <v>92.7</v>
       </c>
       <c r="H772" t="n">
         <v>76</v>
@@ -56699,10 +56081,8 @@
       <c r="F773" t="n">
         <v>74.2</v>
       </c>
-      <c r="G773" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G773" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="H773" t="n">
         <v>70</v>
@@ -56773,10 +56153,8 @@
       <c r="F774" t="n">
         <v>74.2</v>
       </c>
-      <c r="G774" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G774" t="n">
+        <v>91.2</v>
       </c>
       <c r="H774" t="n">
         <v>76</v>
@@ -56847,10 +56225,8 @@
       <c r="F775" t="n">
         <v>74.2</v>
       </c>
-      <c r="G775" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G775" t="n">
+        <v>92.7</v>
       </c>
       <c r="H775" t="n">
         <v>68</v>
@@ -56921,10 +56297,8 @@
       <c r="F776" t="n">
         <v>74.2</v>
       </c>
-      <c r="G776" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G776" t="n">
+        <v>92.7</v>
       </c>
       <c r="H776" t="n">
         <v>68</v>
@@ -56995,10 +56369,8 @@
       <c r="F777" t="n">
         <v>74.2</v>
       </c>
-      <c r="G777" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G777" t="n">
+        <v>92.7</v>
       </c>
       <c r="H777" t="n">
         <v>76</v>
@@ -57069,10 +56441,8 @@
       <c r="F778" t="n">
         <v>74.2</v>
       </c>
-      <c r="G778" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G778" t="n">
+        <v>92.7</v>
       </c>
       <c r="H778" t="n">
         <v>76</v>
@@ -57143,10 +56513,8 @@
       <c r="F779" t="n">
         <v>74.2</v>
       </c>
-      <c r="G779" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G779" t="n">
+        <v>92.7</v>
       </c>
       <c r="H779" t="n">
         <v>76</v>
@@ -57217,10 +56585,8 @@
       <c r="F780" t="n">
         <v>74.2</v>
       </c>
-      <c r="G780" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G780" t="n">
+        <v>92.7</v>
       </c>
       <c r="H780" t="n">
         <v>76</v>
@@ -57291,10 +56657,8 @@
       <c r="F781" t="n">
         <v>74.2</v>
       </c>
-      <c r="G781" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G781" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H781" t="n">
         <v>70</v>
@@ -57365,10 +56729,8 @@
       <c r="F782" t="n">
         <v>74.2</v>
       </c>
-      <c r="G782" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G782" t="n">
+        <v>92.7</v>
       </c>
       <c r="H782" t="n">
         <v>76</v>
@@ -57439,10 +56801,8 @@
       <c r="F783" t="n">
         <v>74.2</v>
       </c>
-      <c r="G783" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G783" t="n">
+        <v>94.3</v>
       </c>
       <c r="H783" t="n">
         <v>76</v>
@@ -57513,10 +56873,8 @@
       <c r="F784" t="n">
         <v>74.2</v>
       </c>
-      <c r="G784" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G784" t="n">
+        <v>91.2</v>
       </c>
       <c r="H784" t="n">
         <v>76</v>
@@ -57587,10 +56945,8 @@
       <c r="F785" t="n">
         <v>74.2</v>
       </c>
-      <c r="G785" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G785" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H785" t="n">
         <v>70</v>
@@ -57661,10 +57017,8 @@
       <c r="F786" t="n">
         <v>74.2</v>
       </c>
-      <c r="G786" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G786" t="n">
+        <v>94.3</v>
       </c>
       <c r="H786" t="n">
         <v>76</v>
@@ -57735,10 +57089,8 @@
       <c r="F787" t="n">
         <v>74.2</v>
       </c>
-      <c r="G787" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G787" t="n">
+        <v>94.3</v>
       </c>
       <c r="H787" t="n">
         <v>68</v>
@@ -57809,10 +57161,8 @@
       <c r="F788" t="n">
         <v>74.2</v>
       </c>
-      <c r="G788" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G788" t="n">
+        <v>92.7</v>
       </c>
       <c r="H788" t="n">
         <v>68</v>
@@ -57883,10 +57233,8 @@
       <c r="F789" t="n">
         <v>74.2</v>
       </c>
-      <c r="G789" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G789" t="n">
+        <v>94.3</v>
       </c>
       <c r="H789" t="n">
         <v>76</v>
@@ -57957,10 +57305,8 @@
       <c r="F790" t="n">
         <v>74.59999999999999</v>
       </c>
-      <c r="G790" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G790" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H790" t="n">
         <v>70</v>
@@ -58031,10 +57377,8 @@
       <c r="F791" t="n">
         <v>74.59999999999999</v>
       </c>
-      <c r="G791" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G791" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="H791" t="n">
         <v>70</v>
@@ -58105,10 +57449,8 @@
       <c r="F792" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G792" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G792" t="n">
+        <v>94.3</v>
       </c>
       <c r="H792" t="n">
         <v>76</v>
@@ -58179,10 +57521,8 @@
       <c r="F793" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G793" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G793" t="n">
+        <v>92.7</v>
       </c>
       <c r="H793" t="n">
         <v>76</v>
@@ -58253,10 +57593,8 @@
       <c r="F794" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G794" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G794" t="n">
+        <v>94.3</v>
       </c>
       <c r="H794" t="n">
         <v>68</v>
@@ -58327,10 +57665,8 @@
       <c r="F795" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G795" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G795" t="n">
+        <v>92.7</v>
       </c>
       <c r="H795" t="n">
         <v>76</v>
@@ -58401,10 +57737,8 @@
       <c r="F796" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G796" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G796" t="n">
+        <v>91.2</v>
       </c>
       <c r="H796" t="n">
         <v>68</v>
@@ -58475,10 +57809,8 @@
       <c r="F797" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G797" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G797" t="n">
+        <v>92.7</v>
       </c>
       <c r="H797" t="n">
         <v>68</v>
@@ -58549,10 +57881,8 @@
       <c r="F798" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G798" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G798" t="n">
+        <v>92.7</v>
       </c>
       <c r="H798" t="n">
         <v>76</v>
@@ -58623,10 +57953,8 @@
       <c r="F799" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G799" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G799" t="n">
+        <v>92.7</v>
       </c>
       <c r="H799" t="n">
         <v>68</v>
@@ -58697,10 +58025,8 @@
       <c r="F800" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G800" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G800" t="n">
+        <v>91.2</v>
       </c>
       <c r="H800" t="n">
         <v>76</v>
@@ -58771,10 +58097,8 @@
       <c r="F801" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G801" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G801" t="n">
+        <v>92.7</v>
       </c>
       <c r="H801" t="n">
         <v>76</v>
@@ -58845,10 +58169,8 @@
       <c r="F802" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G802" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G802" t="n">
+        <v>91.2</v>
       </c>
       <c r="H802" t="n">
         <v>76</v>
@@ -58919,10 +58241,8 @@
       <c r="F803" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G803" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G803" t="n">
+        <v>92.7</v>
       </c>
       <c r="H803" t="n">
         <v>76</v>
@@ -58993,10 +58313,8 @@
       <c r="F804" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G804" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G804" t="n">
+        <v>94.3</v>
       </c>
       <c r="H804" t="n">
         <v>76</v>
@@ -59067,10 +58385,8 @@
       <c r="F805" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G805" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G805" t="n">
+        <v>92.7</v>
       </c>
       <c r="H805" t="n">
         <v>76</v>
@@ -59141,10 +58457,8 @@
       <c r="F806" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G806" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G806" t="n">
+        <v>91.2</v>
       </c>
       <c r="H806" t="n">
         <v>76</v>
@@ -59215,10 +58529,8 @@
       <c r="F807" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G807" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G807" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H807" t="n">
         <v>76</v>
@@ -59289,10 +58601,8 @@
       <c r="F808" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G808" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G808" t="n">
+        <v>92.7</v>
       </c>
       <c r="H808" t="n">
         <v>76</v>
@@ -59363,10 +58673,8 @@
       <c r="F809" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G809" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G809" t="n">
+        <v>92.7</v>
       </c>
       <c r="H809" t="n">
         <v>68</v>
@@ -59437,10 +58745,8 @@
       <c r="F810" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G810" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G810" t="n">
+        <v>92.7</v>
       </c>
       <c r="H810" t="n">
         <v>68</v>
@@ -59511,10 +58817,8 @@
       <c r="F811" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G811" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G811" t="n">
+        <v>92.7</v>
       </c>
       <c r="H811" t="n">
         <v>76</v>
@@ -59585,10 +58889,8 @@
       <c r="F812" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G812" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G812" t="n">
+        <v>88.90000000000001</v>
       </c>
       <c r="H812" t="n">
         <v>70</v>
@@ -59659,10 +58961,8 @@
       <c r="F813" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G813" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G813" t="n">
+        <v>94.3</v>
       </c>
       <c r="H813" t="n">
         <v>76</v>
@@ -59733,10 +59033,8 @@
       <c r="F814" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G814" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G814" t="n">
+        <v>94.3</v>
       </c>
       <c r="H814" t="n">
         <v>68</v>
@@ -59807,10 +59105,8 @@
       <c r="F815" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G815" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G815" t="n">
+        <v>92.7</v>
       </c>
       <c r="H815" t="n">
         <v>68</v>
@@ -59881,10 +59177,8 @@
       <c r="F816" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G816" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G816" t="n">
+        <v>92.7</v>
       </c>
       <c r="H816" t="n">
         <v>76</v>
@@ -59955,10 +59249,8 @@
       <c r="F817" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G817" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G817" t="n">
+        <v>92.7</v>
       </c>
       <c r="H817" t="n">
         <v>76</v>
@@ -60029,10 +59321,8 @@
       <c r="F818" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G818" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G818" t="n">
+        <v>91.2</v>
       </c>
       <c r="H818" t="n">
         <v>76</v>
@@ -60103,10 +59393,8 @@
       <c r="F819" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G819" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G819" t="n">
+        <v>92.7</v>
       </c>
       <c r="H819" t="n">
         <v>68</v>
@@ -60177,10 +59465,8 @@
       <c r="F820" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G820" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G820" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H820" t="n">
         <v>76</v>
@@ -60251,10 +59537,8 @@
       <c r="F821" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G821" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G821" t="n">
+        <v>92.7</v>
       </c>
       <c r="H821" t="n">
         <v>76</v>
@@ -60325,10 +59609,8 @@
       <c r="F822" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G822" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G822" t="n">
+        <v>92.7</v>
       </c>
       <c r="H822" t="n">
         <v>76</v>
@@ -60399,10 +59681,8 @@
       <c r="F823" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G823" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G823" t="n">
+        <v>92.7</v>
       </c>
       <c r="H823" t="n">
         <v>76</v>
@@ -60473,10 +59753,8 @@
       <c r="F824" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G824" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G824" t="n">
+        <v>92.7</v>
       </c>
       <c r="H824" t="n">
         <v>76</v>
@@ -60547,10 +59825,8 @@
       <c r="F825" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G825" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G825" t="n">
+        <v>92.7</v>
       </c>
       <c r="H825" t="n">
         <v>76</v>
@@ -60621,10 +59897,8 @@
       <c r="F826" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G826" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G826" t="n">
+        <v>92.7</v>
       </c>
       <c r="H826" t="n">
         <v>76</v>
@@ -60695,10 +59969,8 @@
       <c r="F827" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G827" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G827" t="n">
+        <v>92.7</v>
       </c>
       <c r="H827" t="n">
         <v>76</v>
@@ -60769,10 +60041,8 @@
       <c r="F828" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G828" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G828" t="n">
+        <v>92.7</v>
       </c>
       <c r="H828" t="n">
         <v>76</v>
@@ -60843,10 +60113,8 @@
       <c r="F829" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G829" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G829" t="n">
+        <v>94.3</v>
       </c>
       <c r="H829" t="n">
         <v>76</v>
@@ -60917,10 +60185,8 @@
       <c r="F830" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G830" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G830" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H830" t="n">
         <v>76</v>
@@ -60991,10 +60257,8 @@
       <c r="F831" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G831" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G831" t="n">
+        <v>92.7</v>
       </c>
       <c r="H831" t="n">
         <v>76</v>
@@ -61065,10 +60329,8 @@
       <c r="F832" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G832" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G832" t="n">
+        <v>92.7</v>
       </c>
       <c r="H832" t="n">
         <v>76</v>
@@ -61139,10 +60401,8 @@
       <c r="F833" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G833" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G833" t="n">
+        <v>94.3</v>
       </c>
       <c r="H833" t="n">
         <v>68</v>
@@ -61213,10 +60473,8 @@
       <c r="F834" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G834" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G834" t="n">
+        <v>91.2</v>
       </c>
       <c r="H834" t="n">
         <v>76</v>
@@ -61287,10 +60545,8 @@
       <c r="F835" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G835" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G835" t="n">
+        <v>92.7</v>
       </c>
       <c r="H835" t="n">
         <v>68</v>
@@ -61361,10 +60617,8 @@
       <c r="F836" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G836" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G836" t="n">
+        <v>92.7</v>
       </c>
       <c r="H836" t="n">
         <v>68</v>
@@ -61435,10 +60689,8 @@
       <c r="F837" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G837" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G837" t="n">
+        <v>91.2</v>
       </c>
       <c r="H837" t="n">
         <v>76</v>
@@ -61509,10 +60761,8 @@
       <c r="F838" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G838" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G838" t="n">
+        <v>91.2</v>
       </c>
       <c r="H838" t="n">
         <v>76</v>
@@ -61583,10 +60833,8 @@
       <c r="F839" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G839" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G839" t="n">
+        <v>94.3</v>
       </c>
       <c r="H839" t="n">
         <v>76</v>
@@ -61657,10 +60905,8 @@
       <c r="F840" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G840" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G840" t="n">
+        <v>94.3</v>
       </c>
       <c r="H840" t="n">
         <v>68</v>
@@ -61731,10 +60977,8 @@
       <c r="F841" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G841" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G841" t="n">
+        <v>92.7</v>
       </c>
       <c r="H841" t="n">
         <v>76</v>
@@ -61805,10 +61049,8 @@
       <c r="F842" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G842" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G842" t="n">
+        <v>92.7</v>
       </c>
       <c r="H842" t="n">
         <v>68</v>
@@ -61879,10 +61121,8 @@
       <c r="F843" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="G843" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G843" t="n">
+        <v>94.3</v>
       </c>
       <c r="H843" t="n">
         <v>76</v>
@@ -61953,10 +61193,8 @@
       <c r="F844" t="n">
         <v>75.8</v>
       </c>
-      <c r="G844" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G844" t="n">
+        <v>94.3</v>
       </c>
       <c r="H844" t="n">
         <v>76</v>
@@ -62027,10 +61265,8 @@
       <c r="F845" t="n">
         <v>75.8</v>
       </c>
-      <c r="G845" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G845" t="n">
+        <v>92.7</v>
       </c>
       <c r="H845" t="n">
         <v>76</v>
@@ -62101,10 +61337,8 @@
       <c r="F846" t="n">
         <v>75.8</v>
       </c>
-      <c r="G846" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G846" t="n">
+        <v>94.3</v>
       </c>
       <c r="H846" t="n">
         <v>76</v>
@@ -62175,10 +61409,8 @@
       <c r="F847" t="n">
         <v>75.8</v>
       </c>
-      <c r="G847" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G847" t="n">
+        <v>94.3</v>
       </c>
       <c r="H847" t="n">
         <v>76</v>
@@ -62249,10 +61481,8 @@
       <c r="F848" t="n">
         <v>75.8</v>
       </c>
-      <c r="G848" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G848" t="n">
+        <v>94.3</v>
       </c>
       <c r="H848" t="n">
         <v>76</v>
@@ -62323,10 +61553,8 @@
       <c r="F849" t="n">
         <v>75.8</v>
       </c>
-      <c r="G849" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G849" t="n">
+        <v>94.3</v>
       </c>
       <c r="H849" t="n">
         <v>76</v>
@@ -62397,10 +61625,8 @@
       <c r="F850" t="n">
         <v>75.8</v>
       </c>
-      <c r="G850" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G850" t="n">
+        <v>92.7</v>
       </c>
       <c r="H850" t="n">
         <v>76</v>
@@ -62471,10 +61697,8 @@
       <c r="F851" t="n">
         <v>75.8</v>
       </c>
-      <c r="G851" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G851" t="n">
+        <v>94.3</v>
       </c>
       <c r="H851" t="n">
         <v>76</v>
@@ -62545,10 +61769,8 @@
       <c r="F852" t="n">
         <v>75.8</v>
       </c>
-      <c r="G852" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G852" t="n">
+        <v>94.3</v>
       </c>
       <c r="H852" t="n">
         <v>76</v>
@@ -62619,10 +61841,8 @@
       <c r="F853" t="n">
         <v>75.8</v>
       </c>
-      <c r="G853" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G853" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H853" t="n">
         <v>70</v>
@@ -62693,10 +61913,8 @@
       <c r="F854" t="n">
         <v>75.8</v>
       </c>
-      <c r="G854" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G854" t="n">
+        <v>94.7</v>
       </c>
       <c r="H854" t="n">
         <v>68</v>
@@ -62767,10 +61985,8 @@
       <c r="F855" t="n">
         <v>75.8</v>
       </c>
-      <c r="G855" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G855" t="n">
+        <v>92.7</v>
       </c>
       <c r="H855" t="n">
         <v>76</v>
@@ -62841,10 +62057,8 @@
       <c r="F856" t="n">
         <v>76.2</v>
       </c>
-      <c r="G856" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G856" t="n">
+        <v>93.5</v>
       </c>
       <c r="H856" t="n">
         <v>70</v>
@@ -62915,10 +62129,8 @@
       <c r="F857" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G857" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G857" t="n">
+        <v>94.3</v>
       </c>
       <c r="H857" t="n">
         <v>76</v>
@@ -62989,10 +62201,8 @@
       <c r="F858" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G858" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G858" t="n">
+        <v>92.7</v>
       </c>
       <c r="H858" t="n">
         <v>76</v>
@@ -63063,10 +62273,8 @@
       <c r="F859" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G859" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G859" t="n">
+        <v>92.7</v>
       </c>
       <c r="H859" t="n">
         <v>76</v>
@@ -63137,10 +62345,8 @@
       <c r="F860" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G860" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G860" t="n">
+        <v>94.3</v>
       </c>
       <c r="H860" t="n">
         <v>76</v>
@@ -63211,10 +62417,8 @@
       <c r="F861" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G861" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G861" t="n">
+        <v>92.7</v>
       </c>
       <c r="H861" t="n">
         <v>76</v>
@@ -63285,10 +62489,8 @@
       <c r="F862" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G862" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G862" t="n">
+        <v>92.7</v>
       </c>
       <c r="H862" t="n">
         <v>76</v>
@@ -63359,10 +62561,8 @@
       <c r="F863" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G863" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G863" t="n">
+        <v>92.7</v>
       </c>
       <c r="H863" t="n">
         <v>76</v>
@@ -63433,10 +62633,8 @@
       <c r="F864" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G864" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G864" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H864" t="n">
         <v>76</v>
@@ -63507,10 +62705,8 @@
       <c r="F865" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G865" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G865" t="n">
+        <v>94.3</v>
       </c>
       <c r="H865" t="n">
         <v>76</v>
@@ -63581,10 +62777,8 @@
       <c r="F866" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G866" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G866" t="n">
+        <v>94.3</v>
       </c>
       <c r="H866" t="n">
         <v>76</v>
@@ -63655,10 +62849,8 @@
       <c r="F867" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G867" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G867" t="n">
+        <v>92.7</v>
       </c>
       <c r="H867" t="n">
         <v>76</v>
@@ -63729,10 +62921,8 @@
       <c r="F868" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G868" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G868" t="n">
+        <v>94.3</v>
       </c>
       <c r="H868" t="n">
         <v>76</v>
@@ -63803,10 +62993,8 @@
       <c r="F869" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G869" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G869" t="n">
+        <v>94.3</v>
       </c>
       <c r="H869" t="n">
         <v>76</v>
@@ -63877,10 +63065,8 @@
       <c r="F870" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G870" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G870" t="n">
+        <v>92.7</v>
       </c>
       <c r="H870" t="n">
         <v>76</v>
@@ -63951,10 +63137,8 @@
       <c r="F871" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G871" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G871" t="n">
+        <v>92.7</v>
       </c>
       <c r="H871" t="n">
         <v>76</v>
@@ -64025,10 +63209,8 @@
       <c r="F872" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G872" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G872" t="n">
+        <v>94.3</v>
       </c>
       <c r="H872" t="n">
         <v>76</v>
@@ -64099,10 +63281,8 @@
       <c r="F873" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G873" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G873" t="n">
+        <v>94.3</v>
       </c>
       <c r="H873" t="n">
         <v>76</v>
@@ -64173,10 +63353,8 @@
       <c r="F874" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G874" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G874" t="n">
+        <v>94.3</v>
       </c>
       <c r="H874" t="n">
         <v>76</v>
@@ -64247,10 +63425,8 @@
       <c r="F875" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G875" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G875" t="n">
+        <v>92.7</v>
       </c>
       <c r="H875" t="n">
         <v>76</v>
@@ -64321,10 +63497,8 @@
       <c r="F876" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G876" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G876" t="n">
+        <v>94.3</v>
       </c>
       <c r="H876" t="n">
         <v>76</v>
@@ -64395,10 +63569,8 @@
       <c r="F877" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G877" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G877" t="n">
+        <v>92.7</v>
       </c>
       <c r="H877" t="n">
         <v>76</v>
@@ -64469,10 +63641,8 @@
       <c r="F878" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G878" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G878" t="n">
+        <v>92.7</v>
       </c>
       <c r="H878" t="n">
         <v>76</v>
@@ -64543,10 +63713,8 @@
       <c r="F879" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G879" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G879" t="n">
+        <v>94.3</v>
       </c>
       <c r="H879" t="n">
         <v>76</v>
@@ -64617,10 +63785,8 @@
       <c r="F880" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G880" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G880" t="n">
+        <v>94.3</v>
       </c>
       <c r="H880" t="n">
         <v>76</v>
@@ -64691,10 +63857,8 @@
       <c r="F881" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G881" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G881" t="n">
+        <v>94.3</v>
       </c>
       <c r="H881" t="n">
         <v>76</v>
@@ -64765,10 +63929,8 @@
       <c r="F882" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G882" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G882" t="n">
+        <v>94.3</v>
       </c>
       <c r="H882" t="n">
         <v>76</v>
@@ -64839,10 +64001,8 @@
       <c r="F883" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G883" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G883" t="n">
+        <v>94.3</v>
       </c>
       <c r="H883" t="n">
         <v>76</v>
@@ -64913,10 +64073,8 @@
       <c r="F884" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G884" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G884" t="n">
+        <v>92.7</v>
       </c>
       <c r="H884" t="n">
         <v>76</v>
@@ -64987,10 +64145,8 @@
       <c r="F885" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G885" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G885" t="n">
+        <v>94.3</v>
       </c>
       <c r="H885" t="n">
         <v>76</v>
@@ -65061,10 +64217,8 @@
       <c r="F886" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G886" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G886" t="n">
+        <v>92.7</v>
       </c>
       <c r="H886" t="n">
         <v>76</v>
@@ -65135,10 +64289,8 @@
       <c r="F887" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G887" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G887" t="n">
+        <v>94.3</v>
       </c>
       <c r="H887" t="n">
         <v>76</v>
@@ -65209,10 +64361,8 @@
       <c r="F888" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G888" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G888" t="n">
+        <v>94.3</v>
       </c>
       <c r="H888" t="n">
         <v>76</v>
@@ -65283,10 +64433,8 @@
       <c r="F889" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G889" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G889" t="n">
+        <v>94.3</v>
       </c>
       <c r="H889" t="n">
         <v>76</v>
@@ -65357,10 +64505,8 @@
       <c r="F890" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G890" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G890" t="n">
+        <v>94.3</v>
       </c>
       <c r="H890" t="n">
         <v>76</v>
@@ -65431,10 +64577,8 @@
       <c r="F891" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G891" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G891" t="n">
+        <v>94.3</v>
       </c>
       <c r="H891" t="n">
         <v>76</v>
@@ -65505,10 +64649,8 @@
       <c r="F892" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G892" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G892" t="n">
+        <v>94.3</v>
       </c>
       <c r="H892" t="n">
         <v>76</v>
@@ -65579,10 +64721,8 @@
       <c r="F893" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G893" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G893" t="n">
+        <v>92.7</v>
       </c>
       <c r="H893" t="n">
         <v>76</v>
@@ -65653,10 +64793,8 @@
       <c r="F894" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G894" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G894" t="n">
+        <v>92.7</v>
       </c>
       <c r="H894" t="n">
         <v>76</v>
@@ -65727,10 +64865,8 @@
       <c r="F895" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G895" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G895" t="n">
+        <v>94.3</v>
       </c>
       <c r="H895" t="n">
         <v>76</v>
@@ -65801,10 +64937,8 @@
       <c r="F896" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G896" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G896" t="n">
+        <v>91.2</v>
       </c>
       <c r="H896" t="n">
         <v>76</v>
@@ -65875,10 +65009,8 @@
       <c r="F897" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G897" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G897" t="n">
+        <v>92.7</v>
       </c>
       <c r="H897" t="n">
         <v>76</v>
@@ -65949,10 +65081,8 @@
       <c r="F898" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G898" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G898" t="n">
+        <v>94.3</v>
       </c>
       <c r="H898" t="n">
         <v>76</v>
@@ -66023,10 +65153,8 @@
       <c r="F899" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G899" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G899" t="n">
+        <v>94.3</v>
       </c>
       <c r="H899" t="n">
         <v>76</v>
@@ -66097,10 +65225,8 @@
       <c r="F900" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G900" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G900" t="n">
+        <v>94.3</v>
       </c>
       <c r="H900" t="n">
         <v>76</v>
@@ -66171,10 +65297,8 @@
       <c r="F901" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G901" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G901" t="n">
+        <v>94.3</v>
       </c>
       <c r="H901" t="n">
         <v>76</v>
@@ -66245,10 +65369,8 @@
       <c r="F902" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G902" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G902" t="n">
+        <v>92.7</v>
       </c>
       <c r="H902" t="n">
         <v>76</v>
@@ -66319,10 +65441,8 @@
       <c r="F903" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G903" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G903" t="n">
+        <v>91.2</v>
       </c>
       <c r="H903" t="n">
         <v>76</v>
@@ -66393,10 +65513,8 @@
       <c r="F904" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G904" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G904" t="n">
+        <v>94.3</v>
       </c>
       <c r="H904" t="n">
         <v>76</v>
@@ -66467,10 +65585,8 @@
       <c r="F905" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G905" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G905" t="n">
+        <v>94.3</v>
       </c>
       <c r="H905" t="n">
         <v>76</v>
@@ -66541,10 +65657,8 @@
       <c r="F906" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G906" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G906" t="n">
+        <v>94.3</v>
       </c>
       <c r="H906" t="n">
         <v>76</v>
@@ -66615,10 +65729,8 @@
       <c r="F907" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G907" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G907" t="n">
+        <v>92.7</v>
       </c>
       <c r="H907" t="n">
         <v>76</v>
@@ -66689,10 +65801,8 @@
       <c r="F908" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G908" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G908" t="n">
+        <v>94.3</v>
       </c>
       <c r="H908" t="n">
         <v>76</v>
@@ -66763,10 +65873,8 @@
       <c r="F909" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G909" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G909" t="n">
+        <v>94.3</v>
       </c>
       <c r="H909" t="n">
         <v>76</v>
@@ -66837,10 +65945,8 @@
       <c r="F910" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G910" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G910" t="n">
+        <v>92.7</v>
       </c>
       <c r="H910" t="n">
         <v>76</v>
@@ -66911,10 +66017,8 @@
       <c r="F911" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G911" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G911" t="n">
+        <v>94.3</v>
       </c>
       <c r="H911" t="n">
         <v>76</v>
@@ -66985,10 +66089,8 @@
       <c r="F912" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G912" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G912" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H912" t="n">
         <v>76</v>
@@ -67059,10 +66161,8 @@
       <c r="F913" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G913" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G913" t="n">
+        <v>92.7</v>
       </c>
       <c r="H913" t="n">
         <v>76</v>
@@ -67133,10 +66233,8 @@
       <c r="F914" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G914" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G914" t="n">
+        <v>92.7</v>
       </c>
       <c r="H914" t="n">
         <v>76</v>
@@ -67207,10 +66305,8 @@
       <c r="F915" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G915" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G915" t="n">
+        <v>94.3</v>
       </c>
       <c r="H915" t="n">
         <v>76</v>
@@ -67281,10 +66377,8 @@
       <c r="F916" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G916" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G916" t="n">
+        <v>94.3</v>
       </c>
       <c r="H916" t="n">
         <v>76</v>
@@ -67355,10 +66449,8 @@
       <c r="F917" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G917" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G917" t="n">
+        <v>94.3</v>
       </c>
       <c r="H917" t="n">
         <v>76</v>
@@ -67429,10 +66521,8 @@
       <c r="F918" t="n">
         <v>77.3</v>
       </c>
-      <c r="G918" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G918" t="n">
+        <v>94.7</v>
       </c>
       <c r="H918" t="n">
         <v>76</v>
@@ -67503,10 +66593,8 @@
       <c r="F919" t="n">
         <v>77.3</v>
       </c>
-      <c r="G919" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G919" t="n">
+        <v>94.7</v>
       </c>
       <c r="H919" t="n">
         <v>76</v>
@@ -67577,10 +66665,8 @@
       <c r="F920" t="n">
         <v>77.3</v>
       </c>
-      <c r="G920" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G920" t="n">
+        <v>94.7</v>
       </c>
       <c r="H920" t="n">
         <v>76</v>
@@ -67651,10 +66737,8 @@
       <c r="F921" t="n">
         <v>77.90000000000001</v>
       </c>
-      <c r="G921" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G921" t="n">
+        <v>77.90000000000001</v>
       </c>
       <c r="H921" t="n">
         <v>94</v>
@@ -67725,10 +66809,8 @@
       <c r="F922" t="n">
         <v>80.90000000000001</v>
       </c>
-      <c r="G922" t="inlineStr">
-        <is>
-          <t>(fish-health: deploy species-app then re-audit)</t>
-        </is>
+      <c r="G922" t="n">
+        <v>80.90000000000001</v>
       </c>
       <c r="H922" t="n">
         <v>78</v>
